--- a/dev_stuffs/4匠魂词条.csv.xlsx
+++ b/dev_stuffs/4匠魂词条.csv.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28730"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28827"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Tony\Documents\EX\HMCL\.minecraft\versions\Palmon\dev_stuffs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{492C3D20-8FA3-40EC-AA45-7BD9D821F895}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5779ACC2-4C98-4651-802B-859BF8329F36}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="12840" yWindow="2250" windowWidth="23940" windowHeight="15435" xr2:uid="{982397F0-7A37-43D3-9AE4-F623F1211744}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21240" xr2:uid="{982397F0-7A37-43D3-9AE4-F623F1211744}"/>
   </bookViews>
   <sheets>
     <sheet name="4匠魂词条" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="629" uniqueCount="623">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="617" uniqueCount="611">
   <si>
     <t>通用：0，工具：1，防御：2，远程：3</t>
   </si>
@@ -325,15 +325,6 @@
     <t>提升工具的耐久度及各项数据！</t>
   </si>
   <si>
-    <t>etstlib:crystal_armor</t>
-  </si>
-  <si>
-    <t>晶质护甲</t>
-  </si>
-  <si>
-    <t>受伤时减少小于5点的伤害，增加大于5点的伤害。</t>
-  </si>
-  <si>
     <t>tconstruct:ricochet</t>
   </si>
   <si>
@@ -343,15 +334,6 @@
     <t>受到攻击时反弹的更远，十分有利于逃跑</t>
   </si>
   <si>
-    <t>tcintegrations:hellish</t>
-  </si>
-  <si>
-    <t>狱火</t>
-  </si>
-  <si>
-    <t>使攻击目标着火。</t>
-  </si>
-  <si>
     <t>tconstruct:lacerating</t>
   </si>
   <si>
@@ -1030,15 +1012,6 @@
     <t>你的挖掘速度固定为工具的挖掘速度，无视挖掘等级。</t>
   </si>
   <si>
-    <t>tcintegrations:precipitate</t>
-  </si>
-  <si>
-    <t>积淀</t>
-  </si>
-  <si>
-    <t>你的生命值越少，它就越快！</t>
-  </si>
-  <si>
     <t>tconstruct:lightweight</t>
   </si>
   <si>
@@ -1622,15 +1595,6 @@
   </si>
   <si>
     <t>攻击者会被困在原地，或者减缓移动速度</t>
-  </si>
-  <si>
-    <t>tinkers_advanced:ender_tuner</t>
-  </si>
-  <si>
-    <t>末影调谐</t>
-  </si>
-  <si>
-    <t>攻击时造成抑影效果，获得50kFE能量存储，损伤时优先消耗能量而非耐久。Shift-右键以打开一个调整页面，可以调节工具的性质。</t>
   </si>
   <si>
     <t>etstlib:short_circuit</t>
@@ -2851,7 +2815,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{66160D17-E746-45B6-B9FC-167F4F38C3EE}">
-  <dimension ref="A1:E210"/>
+  <dimension ref="A1:E206"/>
   <sheetFormatPr defaultRowHeight="18" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="37.5" style="1" customWidth="1"/>
@@ -2884,13 +2848,13 @@
     </row>
     <row r="3" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="1" t="s">
-        <v>122</v>
+        <v>116</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>123</v>
+        <v>117</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>124</v>
+        <v>118</v>
       </c>
       <c r="D3" s="1">
         <v>1</v>
@@ -2918,16 +2882,16 @@
     </row>
     <row r="5" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
-        <v>101</v>
+        <v>11</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>102</v>
+        <v>12</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>103</v>
+        <v>13</v>
       </c>
       <c r="D5" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E5" s="1">
         <v>1</v>
@@ -2935,16 +2899,16 @@
     </row>
     <row r="6" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="1" t="s">
-        <v>11</v>
+        <v>35</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>12</v>
+        <v>36</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>13</v>
+        <v>37</v>
       </c>
       <c r="D6" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E6" s="1">
         <v>1</v>
@@ -2952,13 +2916,13 @@
     </row>
     <row r="7" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="1" t="s">
-        <v>35</v>
+        <v>188</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>36</v>
+        <v>189</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>37</v>
+        <v>190</v>
       </c>
       <c r="D7" s="1">
         <v>1</v>
@@ -2969,16 +2933,16 @@
     </row>
     <row r="8" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="1" t="s">
-        <v>194</v>
+        <v>205</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>195</v>
+        <v>206</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>196</v>
+        <v>207</v>
       </c>
       <c r="D8" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E8" s="1">
         <v>1</v>
@@ -2986,13 +2950,13 @@
     </row>
     <row r="9" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="1" t="s">
-        <v>107</v>
+        <v>41</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>108</v>
+        <v>42</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>109</v>
+        <v>43</v>
       </c>
       <c r="D9" s="1">
         <v>1</v>
@@ -3003,16 +2967,16 @@
     </row>
     <row r="10" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="1" t="s">
-        <v>211</v>
+        <v>77</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>212</v>
+        <v>78</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>213</v>
+        <v>79</v>
       </c>
       <c r="D10" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E10" s="1">
         <v>1</v>
@@ -3020,16 +2984,16 @@
     </row>
     <row r="11" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="1" t="s">
-        <v>41</v>
+        <v>20</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>42</v>
+        <v>21</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>43</v>
+        <v>22</v>
       </c>
       <c r="D11" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E11" s="1">
         <v>1</v>
@@ -3037,13 +3001,13 @@
     </row>
     <row r="12" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="1" t="s">
-        <v>77</v>
+        <v>44</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>78</v>
+        <v>45</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>79</v>
+        <v>46</v>
       </c>
       <c r="D12" s="1">
         <v>1</v>
@@ -3054,16 +3018,16 @@
     </row>
     <row r="13" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="1" t="s">
-        <v>20</v>
+        <v>6</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>21</v>
+        <v>7</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>22</v>
+        <v>8</v>
       </c>
       <c r="D13" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E13" s="1">
         <v>1</v>
@@ -3071,16 +3035,16 @@
     </row>
     <row r="14" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="1" t="s">
-        <v>44</v>
+        <v>197</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>45</v>
+        <v>198</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>46</v>
+        <v>199</v>
       </c>
       <c r="D14" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E14" s="1">
         <v>1</v>
@@ -3088,13 +3052,13 @@
     </row>
     <row r="15" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="1" t="s">
-        <v>6</v>
+        <v>119</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>7</v>
+        <v>120</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>8</v>
+        <v>121</v>
       </c>
       <c r="D15" s="1">
         <v>1</v>
@@ -3105,13 +3069,13 @@
     </row>
     <row r="16" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="1" t="s">
-        <v>203</v>
+        <v>62</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>204</v>
+        <v>63</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>205</v>
+        <v>64</v>
       </c>
       <c r="D16" s="1">
         <v>2</v>
@@ -3122,13 +3086,13 @@
     </row>
     <row r="17" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="1" t="s">
-        <v>125</v>
+        <v>74</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>126</v>
+        <v>75</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>127</v>
+        <v>76</v>
       </c>
       <c r="D17" s="1">
         <v>1</v>
@@ -3139,16 +3103,16 @@
     </row>
     <row r="18" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A18" s="1" t="s">
-        <v>62</v>
+        <v>149</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>63</v>
+        <v>150</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>64</v>
+        <v>151</v>
       </c>
       <c r="D18" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E18" s="1">
         <v>1</v>
@@ -3156,16 +3120,16 @@
     </row>
     <row r="19" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="1" t="s">
-        <v>74</v>
+        <v>140</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>75</v>
+        <v>141</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>76</v>
+        <v>142</v>
       </c>
       <c r="D19" s="1">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E19" s="1">
         <v>1</v>
@@ -3173,16 +3137,16 @@
     </row>
     <row r="20" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A20" s="1" t="s">
-        <v>155</v>
+        <v>146</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>156</v>
+        <v>147</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>157</v>
+        <v>148</v>
       </c>
       <c r="D20" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E20" s="1">
         <v>1</v>
@@ -3190,16 +3154,16 @@
     </row>
     <row r="21" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A21" s="1" t="s">
-        <v>146</v>
+        <v>164</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>147</v>
+        <v>165</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>148</v>
+        <v>166</v>
       </c>
       <c r="D21" s="1">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E21" s="1">
         <v>1</v>
@@ -3207,16 +3171,16 @@
     </row>
     <row r="22" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A22" s="1" t="s">
-        <v>152</v>
+        <v>80</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>153</v>
+        <v>81</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>154</v>
+        <v>82</v>
       </c>
       <c r="D22" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E22" s="1">
         <v>1</v>
@@ -3224,13 +3188,13 @@
     </row>
     <row r="23" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A23" s="1" t="s">
-        <v>170</v>
+        <v>98</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>171</v>
+        <v>99</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>172</v>
+        <v>100</v>
       </c>
       <c r="D23" s="1">
         <v>0</v>
@@ -3241,16 +3205,16 @@
     </row>
     <row r="24" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A24" s="1" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="D24" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E24" s="1">
         <v>1</v>
@@ -3258,13 +3222,13 @@
     </row>
     <row r="25" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A25" s="1" t="s">
-        <v>98</v>
+        <v>56</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>99</v>
+        <v>57</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>100</v>
+        <v>58</v>
       </c>
       <c r="D25" s="1">
         <v>0</v>
@@ -3275,13 +3239,13 @@
     </row>
     <row r="26" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A26" s="1" t="s">
-        <v>83</v>
+        <v>38</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>84</v>
+        <v>39</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>85</v>
+        <v>40</v>
       </c>
       <c r="D26" s="1">
         <v>1</v>
@@ -3292,16 +3256,16 @@
     </row>
     <row r="27" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A27" s="1" t="s">
-        <v>56</v>
+        <v>50</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>57</v>
+        <v>51</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>58</v>
+        <v>52</v>
       </c>
       <c r="D27" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E27" s="1">
         <v>1</v>
@@ -3309,13 +3273,13 @@
     </row>
     <row r="28" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A28" s="1" t="s">
-        <v>38</v>
+        <v>71</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>39</v>
+        <v>72</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>40</v>
+        <v>73</v>
       </c>
       <c r="D28" s="1">
         <v>1</v>
@@ -3326,16 +3290,16 @@
     </row>
     <row r="29" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A29" s="1" t="s">
-        <v>50</v>
+        <v>137</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>51</v>
+        <v>138</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>52</v>
+        <v>139</v>
       </c>
       <c r="D29" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E29" s="1">
         <v>1</v>
@@ -3343,13 +3307,13 @@
     </row>
     <row r="30" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A30" s="1" t="s">
-        <v>71</v>
+        <v>200</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>72</v>
+        <v>189</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>73</v>
+        <v>201</v>
       </c>
       <c r="D30" s="1">
         <v>1</v>
@@ -3360,16 +3324,16 @@
     </row>
     <row r="31" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A31" s="1" t="s">
-        <v>143</v>
+        <v>59</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>144</v>
+        <v>60</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>145</v>
+        <v>61</v>
       </c>
       <c r="D31" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E31" s="1">
         <v>1</v>
@@ -3377,13 +3341,13 @@
     </row>
     <row r="32" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A32" s="1" t="s">
-        <v>206</v>
+        <v>202</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>195</v>
+        <v>203</v>
       </c>
       <c r="C32" s="1" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="D32" s="1">
         <v>1</v>
@@ -3394,16 +3358,16 @@
     </row>
     <row r="33" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A33" s="1" t="s">
-        <v>59</v>
+        <v>107</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>60</v>
+        <v>108</v>
       </c>
       <c r="C33" s="1" t="s">
-        <v>61</v>
+        <v>109</v>
       </c>
       <c r="D33" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E33" s="1">
         <v>1</v>
@@ -3411,13 +3375,13 @@
     </row>
     <row r="34" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A34" s="1" t="s">
-        <v>208</v>
+        <v>182</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>209</v>
+        <v>183</v>
       </c>
       <c r="C34" s="1" t="s">
-        <v>210</v>
+        <v>184</v>
       </c>
       <c r="D34" s="1">
         <v>1</v>
@@ -3428,13 +3392,13 @@
     </row>
     <row r="35" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A35" s="1" t="s">
-        <v>113</v>
+        <v>104</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>114</v>
+        <v>105</v>
       </c>
       <c r="C35" s="1" t="s">
-        <v>115</v>
+        <v>106</v>
       </c>
       <c r="D35" s="1">
         <v>1</v>
@@ -3445,16 +3409,16 @@
     </row>
     <row r="36" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A36" s="1" t="s">
-        <v>188</v>
+        <v>161</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>189</v>
+        <v>162</v>
       </c>
       <c r="C36" s="1" t="s">
-        <v>190</v>
+        <v>163</v>
       </c>
       <c r="D36" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E36" s="1">
         <v>1</v>
@@ -3462,16 +3426,16 @@
     </row>
     <row r="37" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A37" s="1" t="s">
-        <v>110</v>
+        <v>53</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>111</v>
+        <v>54</v>
       </c>
       <c r="C37" s="1" t="s">
-        <v>112</v>
+        <v>55</v>
       </c>
       <c r="D37" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E37" s="1">
         <v>1</v>
@@ -3479,16 +3443,16 @@
     </row>
     <row r="38" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A38" s="1" t="s">
-        <v>167</v>
+        <v>89</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>168</v>
+        <v>90</v>
       </c>
       <c r="C38" s="1" t="s">
-        <v>169</v>
+        <v>91</v>
       </c>
       <c r="D38" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E38" s="1">
         <v>1</v>
@@ -3496,16 +3460,16 @@
     </row>
     <row r="39" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A39" s="1" t="s">
-        <v>53</v>
+        <v>131</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>54</v>
+        <v>132</v>
       </c>
       <c r="C39" s="1" t="s">
-        <v>55</v>
+        <v>133</v>
       </c>
       <c r="D39" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E39" s="1">
         <v>1</v>
@@ -3513,16 +3477,16 @@
     </row>
     <row r="40" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A40" s="1" t="s">
-        <v>89</v>
+        <v>17</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>90</v>
+        <v>18</v>
       </c>
       <c r="C40" s="1" t="s">
-        <v>91</v>
+        <v>19</v>
       </c>
       <c r="D40" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E40" s="1">
         <v>1</v>
@@ -3530,16 +3494,16 @@
     </row>
     <row r="41" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A41" s="1" t="s">
-        <v>137</v>
+        <v>47</v>
       </c>
       <c r="B41" s="1" t="s">
-        <v>138</v>
+        <v>48</v>
       </c>
       <c r="C41" s="1" t="s">
-        <v>139</v>
+        <v>49</v>
       </c>
       <c r="D41" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E41" s="1">
         <v>1</v>
@@ -3547,13 +3511,13 @@
     </row>
     <row r="42" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A42" s="1" t="s">
-        <v>17</v>
+        <v>173</v>
       </c>
       <c r="B42" s="1" t="s">
-        <v>18</v>
+        <v>174</v>
       </c>
       <c r="C42" s="1" t="s">
-        <v>19</v>
+        <v>175</v>
       </c>
       <c r="D42" s="1">
         <v>0</v>
@@ -3564,13 +3528,13 @@
     </row>
     <row r="43" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A43" s="1" t="s">
-        <v>47</v>
+        <v>26</v>
       </c>
       <c r="B43" s="1" t="s">
-        <v>48</v>
+        <v>27</v>
       </c>
       <c r="C43" s="1" t="s">
-        <v>49</v>
+        <v>28</v>
       </c>
       <c r="D43" s="1">
         <v>0</v>
@@ -3581,16 +3545,16 @@
     </row>
     <row r="44" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A44" s="1" t="s">
-        <v>179</v>
+        <v>134</v>
       </c>
       <c r="B44" s="1" t="s">
-        <v>180</v>
+        <v>135</v>
       </c>
       <c r="C44" s="1" t="s">
-        <v>181</v>
+        <v>136</v>
       </c>
       <c r="D44" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E44" s="1">
         <v>1</v>
@@ -3598,16 +3562,16 @@
     </row>
     <row r="45" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A45" s="1" t="s">
-        <v>26</v>
+        <v>170</v>
       </c>
       <c r="B45" s="1" t="s">
-        <v>27</v>
+        <v>171</v>
       </c>
       <c r="C45" s="1" t="s">
-        <v>28</v>
+        <v>172</v>
       </c>
       <c r="D45" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E45" s="1">
         <v>1</v>
@@ -3615,16 +3579,16 @@
     </row>
     <row r="46" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A46" s="1" t="s">
-        <v>140</v>
+        <v>194</v>
       </c>
       <c r="B46" s="1" t="s">
-        <v>141</v>
+        <v>195</v>
       </c>
       <c r="C46" s="1" t="s">
-        <v>142</v>
+        <v>196</v>
       </c>
       <c r="D46" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E46" s="1">
         <v>1</v>
@@ -3632,16 +3596,16 @@
     </row>
     <row r="47" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A47" s="1" t="s">
-        <v>176</v>
+        <v>101</v>
       </c>
       <c r="B47" s="1" t="s">
-        <v>177</v>
+        <v>102</v>
       </c>
       <c r="C47" s="1" t="s">
-        <v>178</v>
+        <v>103</v>
       </c>
       <c r="D47" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E47" s="1">
         <v>1</v>
@@ -3649,13 +3613,13 @@
     </row>
     <row r="48" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A48" s="1" t="s">
-        <v>200</v>
+        <v>191</v>
       </c>
       <c r="B48" s="1" t="s">
-        <v>201</v>
+        <v>192</v>
       </c>
       <c r="C48" s="1" t="s">
-        <v>202</v>
+        <v>193</v>
       </c>
       <c r="D48" s="1">
         <v>2</v>
@@ -3666,16 +3630,16 @@
     </row>
     <row r="49" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A49" s="1" t="s">
-        <v>104</v>
+        <v>176</v>
       </c>
       <c r="B49" s="1" t="s">
-        <v>105</v>
+        <v>177</v>
       </c>
       <c r="C49" s="1" t="s">
-        <v>106</v>
+        <v>178</v>
       </c>
       <c r="D49" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E49" s="1">
         <v>1</v>
@@ -3683,16 +3647,16 @@
     </row>
     <row r="50" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A50" s="1" t="s">
-        <v>197</v>
+        <v>68</v>
       </c>
       <c r="B50" s="1" t="s">
-        <v>198</v>
+        <v>69</v>
       </c>
       <c r="C50" s="1" t="s">
-        <v>199</v>
+        <v>70</v>
       </c>
       <c r="D50" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E50" s="1">
         <v>1</v>
@@ -3700,13 +3664,13 @@
     </row>
     <row r="51" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A51" s="1" t="s">
-        <v>182</v>
+        <v>110</v>
       </c>
       <c r="B51" s="1" t="s">
-        <v>183</v>
+        <v>111</v>
       </c>
       <c r="C51" s="1" t="s">
-        <v>184</v>
+        <v>112</v>
       </c>
       <c r="D51" s="1">
         <v>1</v>
@@ -3717,13 +3681,13 @@
     </row>
     <row r="52" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A52" s="1" t="s">
-        <v>68</v>
+        <v>158</v>
       </c>
       <c r="B52" s="1" t="s">
-        <v>69</v>
+        <v>159</v>
       </c>
       <c r="C52" s="1" t="s">
-        <v>70</v>
+        <v>160</v>
       </c>
       <c r="D52" s="1">
         <v>0</v>
@@ -3734,13 +3698,13 @@
     </row>
     <row r="53" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A53" s="1" t="s">
-        <v>116</v>
+        <v>122</v>
       </c>
       <c r="B53" s="1" t="s">
-        <v>117</v>
+        <v>123</v>
       </c>
       <c r="C53" s="1" t="s">
-        <v>118</v>
+        <v>124</v>
       </c>
       <c r="D53" s="1">
         <v>1</v>
@@ -3751,13 +3715,13 @@
     </row>
     <row r="54" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A54" s="1" t="s">
-        <v>164</v>
+        <v>143</v>
       </c>
       <c r="B54" s="1" t="s">
-        <v>165</v>
+        <v>144</v>
       </c>
       <c r="C54" s="1" t="s">
-        <v>166</v>
+        <v>145</v>
       </c>
       <c r="D54" s="1">
         <v>0</v>
@@ -3768,13 +3732,13 @@
     </row>
     <row r="55" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A55" s="1" t="s">
-        <v>128</v>
+        <v>179</v>
       </c>
       <c r="B55" s="1" t="s">
-        <v>129</v>
+        <v>180</v>
       </c>
       <c r="C55" s="1" t="s">
-        <v>130</v>
+        <v>181</v>
       </c>
       <c r="D55" s="1">
         <v>1</v>
@@ -3785,13 +3749,13 @@
     </row>
     <row r="56" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A56" s="1" t="s">
-        <v>149</v>
+        <v>86</v>
       </c>
       <c r="B56" s="1" t="s">
-        <v>150</v>
+        <v>87</v>
       </c>
       <c r="C56" s="1" t="s">
-        <v>151</v>
+        <v>88</v>
       </c>
       <c r="D56" s="1">
         <v>0</v>
@@ -3811,7 +3775,7 @@
         <v>187</v>
       </c>
       <c r="D57" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E57" s="1">
         <v>1</v>
@@ -3819,13 +3783,13 @@
     </row>
     <row r="58" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A58" s="1" t="s">
-        <v>86</v>
+        <v>65</v>
       </c>
       <c r="B58" s="1" t="s">
-        <v>87</v>
+        <v>66</v>
       </c>
       <c r="C58" s="1" t="s">
-        <v>88</v>
+        <v>67</v>
       </c>
       <c r="D58" s="1">
         <v>0</v>
@@ -3836,16 +3800,16 @@
     </row>
     <row r="59" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A59" s="1" t="s">
-        <v>191</v>
+        <v>152</v>
       </c>
       <c r="B59" s="1" t="s">
-        <v>192</v>
+        <v>153</v>
       </c>
       <c r="C59" s="1" t="s">
-        <v>193</v>
+        <v>154</v>
       </c>
       <c r="D59" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E59" s="1">
         <v>1</v>
@@ -3853,16 +3817,16 @@
     </row>
     <row r="60" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A60" s="1" t="s">
-        <v>65</v>
+        <v>23</v>
       </c>
       <c r="B60" s="1" t="s">
-        <v>66</v>
+        <v>24</v>
       </c>
       <c r="C60" s="1" t="s">
-        <v>67</v>
+        <v>25</v>
       </c>
       <c r="D60" s="1">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E60" s="1">
         <v>1</v>
@@ -3870,13 +3834,13 @@
     </row>
     <row r="61" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A61" s="1" t="s">
-        <v>158</v>
+        <v>113</v>
       </c>
       <c r="B61" s="1" t="s">
-        <v>159</v>
+        <v>114</v>
       </c>
       <c r="C61" s="1" t="s">
-        <v>160</v>
+        <v>115</v>
       </c>
       <c r="D61" s="1">
         <v>1</v>
@@ -3887,16 +3851,16 @@
     </row>
     <row r="62" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A62" s="1" t="s">
-        <v>23</v>
+        <v>208</v>
       </c>
       <c r="B62" s="1" t="s">
-        <v>24</v>
+        <v>209</v>
       </c>
       <c r="C62" s="1" t="s">
-        <v>25</v>
+        <v>210</v>
       </c>
       <c r="D62" s="1">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E62" s="1">
         <v>1</v>
@@ -3904,16 +3868,16 @@
     </row>
     <row r="63" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A63" s="1" t="s">
-        <v>119</v>
+        <v>155</v>
       </c>
       <c r="B63" s="1" t="s">
-        <v>120</v>
+        <v>156</v>
       </c>
       <c r="C63" s="1" t="s">
-        <v>121</v>
+        <v>157</v>
       </c>
       <c r="D63" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E63" s="1">
         <v>1</v>
@@ -3921,13 +3885,10 @@
     </row>
     <row r="64" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A64" s="1" t="s">
-        <v>214</v>
-      </c>
-      <c r="B64" s="1" t="s">
-        <v>215</v>
+        <v>9</v>
       </c>
       <c r="C64" s="1" t="s">
-        <v>216</v>
+        <v>10</v>
       </c>
       <c r="D64" s="1">
         <v>0</v>
@@ -3938,13 +3899,13 @@
     </row>
     <row r="65" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A65" s="1" t="s">
-        <v>161</v>
+        <v>32</v>
       </c>
       <c r="B65" s="1" t="s">
-        <v>162</v>
+        <v>33</v>
       </c>
       <c r="C65" s="1" t="s">
-        <v>163</v>
+        <v>34</v>
       </c>
       <c r="D65" s="1">
         <v>0</v>
@@ -3955,10 +3916,13 @@
     </row>
     <row r="66" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A66" s="1" t="s">
-        <v>9</v>
+        <v>92</v>
+      </c>
+      <c r="B66" s="1" t="s">
+        <v>93</v>
       </c>
       <c r="C66" s="1" t="s">
-        <v>10</v>
+        <v>94</v>
       </c>
       <c r="D66" s="1">
         <v>0</v>
@@ -3969,13 +3933,13 @@
     </row>
     <row r="67" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A67" s="1" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="B67" s="1" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="C67" s="1" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="D67" s="1">
         <v>0</v>
@@ -3986,16 +3950,16 @@
     </row>
     <row r="68" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A68" s="1" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="B68" s="1" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="C68" s="1" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="D68" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E68" s="1">
         <v>1</v>
@@ -4003,13 +3967,13 @@
     </row>
     <row r="69" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A69" s="1" t="s">
-        <v>29</v>
+        <v>167</v>
       </c>
       <c r="B69" s="1" t="s">
-        <v>30</v>
+        <v>168</v>
       </c>
       <c r="C69" s="1" t="s">
-        <v>31</v>
+        <v>169</v>
       </c>
       <c r="D69" s="1">
         <v>0</v>
@@ -4020,13 +3984,13 @@
     </row>
     <row r="70" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A70" s="1" t="s">
-        <v>95</v>
+        <v>128</v>
       </c>
       <c r="B70" s="1" t="s">
-        <v>96</v>
+        <v>129</v>
       </c>
       <c r="C70" s="1" t="s">
-        <v>97</v>
+        <v>130</v>
       </c>
       <c r="D70" s="1">
         <v>1</v>
@@ -4037,16 +4001,16 @@
     </row>
     <row r="71" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A71" s="1" t="s">
-        <v>173</v>
+        <v>125</v>
       </c>
       <c r="B71" s="1" t="s">
-        <v>174</v>
+        <v>126</v>
       </c>
       <c r="C71" s="1" t="s">
-        <v>175</v>
+        <v>127</v>
       </c>
       <c r="D71" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E71" s="1">
         <v>1</v>
@@ -4054,47 +4018,47 @@
     </row>
     <row r="72" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A72" s="1" t="s">
-        <v>134</v>
+        <v>235</v>
       </c>
       <c r="B72" s="1" t="s">
-        <v>135</v>
+        <v>236</v>
       </c>
       <c r="C72" s="1" t="s">
-        <v>136</v>
+        <v>237</v>
       </c>
       <c r="D72" s="1">
         <v>1</v>
       </c>
       <c r="E72" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="73" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A73" s="1" t="s">
-        <v>131</v>
+        <v>327</v>
       </c>
       <c r="B73" s="1" t="s">
-        <v>132</v>
+        <v>328</v>
       </c>
       <c r="C73" s="1" t="s">
-        <v>133</v>
+        <v>329</v>
       </c>
       <c r="D73" s="1">
         <v>1</v>
       </c>
       <c r="E73" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="74" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A74" s="1" t="s">
-        <v>241</v>
+        <v>312</v>
       </c>
       <c r="B74" s="1" t="s">
-        <v>242</v>
+        <v>313</v>
       </c>
       <c r="C74" s="1" t="s">
-        <v>243</v>
+        <v>314</v>
       </c>
       <c r="D74" s="1">
         <v>1</v>
@@ -4105,16 +4069,16 @@
     </row>
     <row r="75" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A75" s="1" t="s">
-        <v>333</v>
+        <v>412</v>
       </c>
       <c r="B75" s="1" t="s">
-        <v>334</v>
+        <v>413</v>
       </c>
       <c r="C75" s="1" t="s">
-        <v>335</v>
+        <v>414</v>
       </c>
       <c r="D75" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E75" s="1">
         <v>2</v>
@@ -4122,13 +4086,13 @@
     </row>
     <row r="76" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A76" s="1" t="s">
-        <v>318</v>
+        <v>463</v>
       </c>
       <c r="B76" s="1" t="s">
-        <v>319</v>
+        <v>464</v>
       </c>
       <c r="C76" s="1" t="s">
-        <v>320</v>
+        <v>465</v>
       </c>
       <c r="D76" s="1">
         <v>1</v>
@@ -4139,16 +4103,16 @@
     </row>
     <row r="77" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A77" s="1" t="s">
-        <v>421</v>
+        <v>363</v>
       </c>
       <c r="B77" s="1" t="s">
-        <v>422</v>
+        <v>364</v>
       </c>
       <c r="C77" s="1" t="s">
-        <v>423</v>
+        <v>365</v>
       </c>
       <c r="D77" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E77" s="1">
         <v>2</v>
@@ -4156,16 +4120,16 @@
     </row>
     <row r="78" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A78" s="1" t="s">
-        <v>472</v>
+        <v>324</v>
       </c>
       <c r="B78" s="1" t="s">
-        <v>473</v>
+        <v>325</v>
       </c>
       <c r="C78" s="1" t="s">
-        <v>474</v>
+        <v>326</v>
       </c>
       <c r="D78" s="1">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E78" s="1">
         <v>2</v>
@@ -4173,13 +4137,13 @@
     </row>
     <row r="79" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A79" s="1" t="s">
-        <v>372</v>
+        <v>354</v>
       </c>
       <c r="B79" s="1" t="s">
-        <v>373</v>
+        <v>355</v>
       </c>
       <c r="C79" s="1" t="s">
-        <v>374</v>
+        <v>356</v>
       </c>
       <c r="D79" s="1">
         <v>2</v>
@@ -4190,16 +4154,16 @@
     </row>
     <row r="80" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A80" s="1" t="s">
-        <v>330</v>
+        <v>366</v>
       </c>
       <c r="B80" s="1" t="s">
-        <v>331</v>
+        <v>367</v>
       </c>
       <c r="C80" s="1" t="s">
-        <v>332</v>
+        <v>368</v>
       </c>
       <c r="D80" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E80" s="1">
         <v>2</v>
@@ -4207,13 +4171,13 @@
     </row>
     <row r="81" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A81" s="1" t="s">
-        <v>363</v>
+        <v>250</v>
       </c>
       <c r="B81" s="1" t="s">
-        <v>364</v>
+        <v>251</v>
       </c>
       <c r="C81" s="1" t="s">
-        <v>365</v>
+        <v>252</v>
       </c>
       <c r="D81" s="1">
         <v>2</v>
@@ -4224,16 +4188,16 @@
     </row>
     <row r="82" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A82" s="1" t="s">
-        <v>375</v>
+        <v>398</v>
       </c>
       <c r="B82" s="1" t="s">
-        <v>376</v>
+        <v>399</v>
       </c>
       <c r="C82" s="1" t="s">
-        <v>377</v>
+        <v>400</v>
       </c>
       <c r="D82" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E82" s="1">
         <v>2</v>
@@ -4241,13 +4205,13 @@
     </row>
     <row r="83" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A83" s="1" t="s">
-        <v>256</v>
+        <v>279</v>
       </c>
       <c r="B83" s="1" t="s">
-        <v>257</v>
+        <v>280</v>
       </c>
       <c r="C83" s="1" t="s">
-        <v>258</v>
+        <v>281</v>
       </c>
       <c r="D83" s="1">
         <v>2</v>
@@ -4258,13 +4222,13 @@
     </row>
     <row r="84" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A84" s="1" t="s">
-        <v>407</v>
+        <v>457</v>
       </c>
       <c r="B84" s="1" t="s">
-        <v>408</v>
+        <v>458</v>
       </c>
       <c r="C84" s="1" t="s">
-        <v>409</v>
+        <v>459</v>
       </c>
       <c r="D84" s="1">
         <v>1</v>
@@ -4292,13 +4256,13 @@
     </row>
     <row r="86" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A86" s="1" t="s">
-        <v>466</v>
+        <v>294</v>
       </c>
       <c r="B86" s="1" t="s">
-        <v>467</v>
+        <v>295</v>
       </c>
       <c r="C86" s="1" t="s">
-        <v>468</v>
+        <v>296</v>
       </c>
       <c r="D86" s="1">
         <v>1</v>
@@ -4309,16 +4273,16 @@
     </row>
     <row r="87" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A87" s="1" t="s">
-        <v>291</v>
+        <v>300</v>
       </c>
       <c r="B87" s="1" t="s">
-        <v>292</v>
+        <v>301</v>
       </c>
       <c r="C87" s="1" t="s">
-        <v>293</v>
+        <v>302</v>
       </c>
       <c r="D87" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E87" s="1">
         <v>2</v>
@@ -4326,16 +4290,16 @@
     </row>
     <row r="88" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A88" s="1" t="s">
-        <v>300</v>
+        <v>273</v>
       </c>
       <c r="B88" s="1" t="s">
-        <v>301</v>
+        <v>274</v>
       </c>
       <c r="C88" s="1" t="s">
-        <v>302</v>
+        <v>275</v>
       </c>
       <c r="D88" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E88" s="1">
         <v>2</v>
@@ -4343,16 +4307,16 @@
     </row>
     <row r="89" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A89" s="1" t="s">
-        <v>306</v>
+        <v>466</v>
       </c>
       <c r="B89" s="1" t="s">
-        <v>307</v>
+        <v>467</v>
       </c>
       <c r="C89" s="1" t="s">
-        <v>308</v>
+        <v>468</v>
       </c>
       <c r="D89" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E89" s="1">
         <v>2</v>
@@ -4360,13 +4324,13 @@
     </row>
     <row r="90" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A90" s="1" t="s">
-        <v>279</v>
+        <v>430</v>
       </c>
       <c r="B90" s="1" t="s">
-        <v>280</v>
+        <v>431</v>
       </c>
       <c r="C90" s="1" t="s">
-        <v>281</v>
+        <v>432</v>
       </c>
       <c r="D90" s="1">
         <v>2</v>
@@ -4377,13 +4341,13 @@
     </row>
     <row r="91" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A91" s="1" t="s">
-        <v>336</v>
+        <v>276</v>
       </c>
       <c r="B91" s="1" t="s">
-        <v>337</v>
+        <v>277</v>
       </c>
       <c r="C91" s="1" t="s">
-        <v>338</v>
+        <v>278</v>
       </c>
       <c r="D91" s="1">
         <v>1</v>
@@ -4394,16 +4358,16 @@
     </row>
     <row r="92" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A92" s="1" t="s">
-        <v>475</v>
+        <v>454</v>
       </c>
       <c r="B92" s="1" t="s">
-        <v>476</v>
+        <v>455</v>
       </c>
       <c r="C92" s="1" t="s">
-        <v>477</v>
+        <v>456</v>
       </c>
       <c r="D92" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E92" s="1">
         <v>2</v>
@@ -4428,16 +4392,16 @@
     </row>
     <row r="94" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A94" s="1" t="s">
-        <v>282</v>
+        <v>267</v>
       </c>
       <c r="B94" s="1" t="s">
-        <v>283</v>
+        <v>268</v>
       </c>
       <c r="C94" s="1" t="s">
-        <v>284</v>
+        <v>269</v>
       </c>
       <c r="D94" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E94" s="1">
         <v>2</v>
@@ -4445,13 +4409,13 @@
     </row>
     <row r="95" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A95" s="1" t="s">
-        <v>463</v>
+        <v>375</v>
       </c>
       <c r="B95" s="1" t="s">
-        <v>464</v>
+        <v>376</v>
       </c>
       <c r="C95" s="1" t="s">
-        <v>465</v>
+        <v>377</v>
       </c>
       <c r="D95" s="1">
         <v>1</v>
@@ -4462,16 +4426,16 @@
     </row>
     <row r="96" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A96" s="1" t="s">
-        <v>448</v>
+        <v>217</v>
       </c>
       <c r="B96" s="1" t="s">
-        <v>449</v>
+        <v>218</v>
       </c>
       <c r="C96" s="1" t="s">
-        <v>450</v>
+        <v>219</v>
       </c>
       <c r="D96" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E96" s="1">
         <v>2</v>
@@ -4479,13 +4443,13 @@
     </row>
     <row r="97" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A97" s="1" t="s">
-        <v>273</v>
+        <v>387</v>
       </c>
       <c r="B97" s="1" t="s">
-        <v>274</v>
+        <v>227</v>
       </c>
       <c r="C97" s="1" t="s">
-        <v>275</v>
+        <v>388</v>
       </c>
       <c r="D97" s="1">
         <v>2</v>
@@ -4496,16 +4460,16 @@
     </row>
     <row r="98" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A98" s="1" t="s">
-        <v>384</v>
+        <v>442</v>
       </c>
       <c r="B98" s="1" t="s">
-        <v>385</v>
+        <v>443</v>
       </c>
       <c r="C98" s="1" t="s">
-        <v>386</v>
+        <v>444</v>
       </c>
       <c r="D98" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E98" s="1">
         <v>2</v>
@@ -4513,16 +4477,16 @@
     </row>
     <row r="99" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A99" s="1" t="s">
-        <v>223</v>
+        <v>232</v>
       </c>
       <c r="B99" s="1" t="s">
-        <v>224</v>
+        <v>233</v>
       </c>
       <c r="C99" s="1" t="s">
-        <v>225</v>
+        <v>234</v>
       </c>
       <c r="D99" s="1">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E99" s="1">
         <v>2</v>
@@ -4530,16 +4494,16 @@
     </row>
     <row r="100" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A100" s="1" t="s">
-        <v>396</v>
+        <v>342</v>
       </c>
       <c r="B100" s="1" t="s">
-        <v>233</v>
+        <v>343</v>
       </c>
       <c r="C100" s="1" t="s">
-        <v>397</v>
+        <v>344</v>
       </c>
       <c r="D100" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E100" s="1">
         <v>2</v>
@@ -4547,13 +4511,13 @@
     </row>
     <row r="101" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A101" s="1" t="s">
-        <v>451</v>
+        <v>247</v>
       </c>
       <c r="B101" s="1" t="s">
-        <v>452</v>
+        <v>248</v>
       </c>
       <c r="C101" s="1" t="s">
-        <v>453</v>
+        <v>249</v>
       </c>
       <c r="D101" s="1">
         <v>2</v>
@@ -4564,16 +4528,16 @@
     </row>
     <row r="102" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A102" s="1" t="s">
-        <v>238</v>
+        <v>418</v>
       </c>
       <c r="B102" s="1" t="s">
-        <v>239</v>
+        <v>419</v>
       </c>
       <c r="C102" s="1" t="s">
-        <v>240</v>
+        <v>420</v>
       </c>
       <c r="D102" s="1">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E102" s="1">
         <v>2</v>
@@ -4581,16 +4545,16 @@
     </row>
     <row r="103" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A103" s="1" t="s">
-        <v>351</v>
+        <v>436</v>
       </c>
       <c r="B103" s="1" t="s">
-        <v>352</v>
+        <v>437</v>
       </c>
       <c r="C103" s="1" t="s">
-        <v>353</v>
+        <v>438</v>
       </c>
       <c r="D103" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E103" s="1">
         <v>2</v>
@@ -4598,16 +4562,16 @@
     </row>
     <row r="104" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A104" s="1" t="s">
-        <v>253</v>
+        <v>406</v>
       </c>
       <c r="B104" s="1" t="s">
-        <v>254</v>
+        <v>407</v>
       </c>
       <c r="C104" s="1" t="s">
-        <v>255</v>
+        <v>408</v>
       </c>
       <c r="D104" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E104" s="1">
         <v>2</v>
@@ -4615,13 +4579,13 @@
     </row>
     <row r="105" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A105" s="1" t="s">
-        <v>427</v>
+        <v>369</v>
       </c>
       <c r="B105" s="1" t="s">
-        <v>428</v>
+        <v>370</v>
       </c>
       <c r="C105" s="1" t="s">
-        <v>429</v>
+        <v>371</v>
       </c>
       <c r="D105" s="1">
         <v>0</v>
@@ -4632,16 +4596,16 @@
     </row>
     <row r="106" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A106" s="1" t="s">
-        <v>445</v>
+        <v>372</v>
       </c>
       <c r="B106" s="1" t="s">
-        <v>446</v>
+        <v>373</v>
       </c>
       <c r="C106" s="1" t="s">
-        <v>447</v>
+        <v>374</v>
       </c>
       <c r="D106" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E106" s="1">
         <v>2</v>
@@ -4649,13 +4613,13 @@
     </row>
     <row r="107" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A107" s="1" t="s">
-        <v>415</v>
+        <v>392</v>
       </c>
       <c r="B107" s="1" t="s">
-        <v>416</v>
+        <v>393</v>
       </c>
       <c r="C107" s="1" t="s">
-        <v>417</v>
+        <v>394</v>
       </c>
       <c r="D107" s="1">
         <v>1</v>
@@ -4666,13 +4630,13 @@
     </row>
     <row r="108" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A108" s="1" t="s">
-        <v>378</v>
+        <v>415</v>
       </c>
       <c r="B108" s="1" t="s">
-        <v>379</v>
+        <v>416</v>
       </c>
       <c r="C108" s="1" t="s">
-        <v>380</v>
+        <v>417</v>
       </c>
       <c r="D108" s="1">
         <v>0</v>
@@ -4683,16 +4647,16 @@
     </row>
     <row r="109" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A109" s="1" t="s">
-        <v>381</v>
+        <v>445</v>
       </c>
       <c r="B109" s="1" t="s">
-        <v>382</v>
+        <v>446</v>
       </c>
       <c r="C109" s="1" t="s">
-        <v>383</v>
+        <v>447</v>
       </c>
       <c r="D109" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E109" s="1">
         <v>2</v>
@@ -4700,16 +4664,16 @@
     </row>
     <row r="110" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A110" s="1" t="s">
-        <v>401</v>
+        <v>214</v>
       </c>
       <c r="B110" s="1" t="s">
-        <v>402</v>
+        <v>215</v>
       </c>
       <c r="C110" s="1" t="s">
-        <v>403</v>
+        <v>216</v>
       </c>
       <c r="D110" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E110" s="1">
         <v>2</v>
@@ -4717,16 +4681,16 @@
     </row>
     <row r="111" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A111" s="1" t="s">
-        <v>424</v>
+        <v>220</v>
       </c>
       <c r="B111" s="1" t="s">
-        <v>425</v>
+        <v>221</v>
       </c>
       <c r="C111" s="1" t="s">
-        <v>426</v>
+        <v>222</v>
       </c>
       <c r="D111" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E111" s="1">
         <v>2</v>
@@ -4734,13 +4698,13 @@
     </row>
     <row r="112" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A112" s="1" t="s">
-        <v>454</v>
+        <v>460</v>
       </c>
       <c r="B112" s="1" t="s">
-        <v>455</v>
+        <v>461</v>
       </c>
       <c r="C112" s="1" t="s">
-        <v>456</v>
+        <v>462</v>
       </c>
       <c r="D112" s="1">
         <v>0</v>
@@ -4751,16 +4715,16 @@
     </row>
     <row r="113" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A113" s="1" t="s">
-        <v>220</v>
+        <v>297</v>
       </c>
       <c r="B113" s="1" t="s">
-        <v>221</v>
+        <v>298</v>
       </c>
       <c r="C113" s="1" t="s">
-        <v>222</v>
+        <v>299</v>
       </c>
       <c r="D113" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E113" s="1">
         <v>2</v>
@@ -4768,16 +4732,16 @@
     </row>
     <row r="114" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A114" s="1" t="s">
-        <v>226</v>
+        <v>384</v>
       </c>
       <c r="B114" s="1" t="s">
-        <v>227</v>
+        <v>385</v>
       </c>
       <c r="C114" s="1" t="s">
-        <v>228</v>
+        <v>386</v>
       </c>
       <c r="D114" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E114" s="1">
         <v>2</v>
@@ -4785,16 +4749,16 @@
     </row>
     <row r="115" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A115" s="1" t="s">
-        <v>469</v>
+        <v>378</v>
       </c>
       <c r="B115" s="1" t="s">
-        <v>470</v>
+        <v>379</v>
       </c>
       <c r="C115" s="1" t="s">
-        <v>471</v>
+        <v>380</v>
       </c>
       <c r="D115" s="1">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E115" s="1">
         <v>2</v>
@@ -4802,13 +4766,13 @@
     </row>
     <row r="116" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A116" s="1" t="s">
-        <v>303</v>
+        <v>226</v>
       </c>
       <c r="B116" s="1" t="s">
-        <v>304</v>
+        <v>227</v>
       </c>
       <c r="C116" s="1" t="s">
-        <v>305</v>
+        <v>228</v>
       </c>
       <c r="D116" s="1">
         <v>1</v>
@@ -4819,16 +4783,16 @@
     </row>
     <row r="117" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A117" s="1" t="s">
-        <v>393</v>
+        <v>238</v>
       </c>
       <c r="B117" s="1" t="s">
-        <v>394</v>
+        <v>239</v>
       </c>
       <c r="C117" s="1" t="s">
-        <v>395</v>
+        <v>240</v>
       </c>
       <c r="D117" s="1">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E117" s="1">
         <v>2</v>
@@ -4836,16 +4800,16 @@
     </row>
     <row r="118" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A118" s="1" t="s">
-        <v>387</v>
+        <v>330</v>
       </c>
       <c r="B118" s="1" t="s">
-        <v>388</v>
+        <v>331</v>
       </c>
       <c r="C118" s="1" t="s">
-        <v>389</v>
+        <v>332</v>
       </c>
       <c r="D118" s="1">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E118" s="1">
         <v>2</v>
@@ -4853,16 +4817,16 @@
     </row>
     <row r="119" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A119" s="1" t="s">
-        <v>232</v>
+        <v>448</v>
       </c>
       <c r="B119" s="1" t="s">
-        <v>233</v>
+        <v>449</v>
       </c>
       <c r="C119" s="1" t="s">
-        <v>234</v>
+        <v>450</v>
       </c>
       <c r="D119" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E119" s="1">
         <v>2</v>
@@ -4870,16 +4834,16 @@
     </row>
     <row r="120" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A120" s="1" t="s">
-        <v>244</v>
+        <v>270</v>
       </c>
       <c r="B120" s="1" t="s">
-        <v>245</v>
+        <v>271</v>
       </c>
       <c r="C120" s="1" t="s">
-        <v>246</v>
+        <v>272</v>
       </c>
       <c r="D120" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E120" s="1">
         <v>2</v>
@@ -4887,13 +4851,13 @@
     </row>
     <row r="121" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A121" s="1" t="s">
-        <v>339</v>
+        <v>303</v>
       </c>
       <c r="B121" s="1" t="s">
-        <v>340</v>
+        <v>304</v>
       </c>
       <c r="C121" s="1" t="s">
-        <v>341</v>
+        <v>305</v>
       </c>
       <c r="D121" s="1">
         <v>1</v>
@@ -4904,13 +4868,13 @@
     </row>
     <row r="122" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A122" s="1" t="s">
-        <v>457</v>
+        <v>433</v>
       </c>
       <c r="B122" s="1" t="s">
-        <v>458</v>
+        <v>434</v>
       </c>
       <c r="C122" s="1" t="s">
-        <v>459</v>
+        <v>435</v>
       </c>
       <c r="D122" s="1">
         <v>2</v>
@@ -4921,16 +4885,16 @@
     </row>
     <row r="123" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A123" s="1" t="s">
-        <v>276</v>
+        <v>421</v>
       </c>
       <c r="B123" s="1" t="s">
-        <v>277</v>
+        <v>422</v>
       </c>
       <c r="C123" s="1" t="s">
-        <v>278</v>
+        <v>423</v>
       </c>
       <c r="D123" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E123" s="1">
         <v>2</v>
@@ -4938,16 +4902,16 @@
     </row>
     <row r="124" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A124" s="1" t="s">
-        <v>309</v>
+        <v>244</v>
       </c>
       <c r="B124" s="1" t="s">
-        <v>310</v>
+        <v>245</v>
       </c>
       <c r="C124" s="1" t="s">
-        <v>311</v>
+        <v>246</v>
       </c>
       <c r="D124" s="1">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E124" s="1">
         <v>2</v>
@@ -4955,16 +4919,16 @@
     </row>
     <row r="125" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A125" s="1" t="s">
-        <v>442</v>
+        <v>223</v>
       </c>
       <c r="B125" s="1" t="s">
-        <v>443</v>
+        <v>224</v>
       </c>
       <c r="C125" s="1" t="s">
-        <v>444</v>
+        <v>225</v>
       </c>
       <c r="D125" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E125" s="1">
         <v>2</v>
@@ -4972,16 +4936,16 @@
     </row>
     <row r="126" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A126" s="1" t="s">
-        <v>430</v>
+        <v>424</v>
       </c>
       <c r="B126" s="1" t="s">
-        <v>431</v>
+        <v>425</v>
       </c>
       <c r="C126" s="1" t="s">
-        <v>432</v>
+        <v>426</v>
       </c>
       <c r="D126" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E126" s="1">
         <v>2</v>
@@ -4989,16 +4953,16 @@
     </row>
     <row r="127" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A127" s="1" t="s">
-        <v>250</v>
+        <v>291</v>
       </c>
       <c r="B127" s="1" t="s">
-        <v>251</v>
+        <v>292</v>
       </c>
       <c r="C127" s="1" t="s">
-        <v>252</v>
+        <v>293</v>
       </c>
       <c r="D127" s="1">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E127" s="1">
         <v>2</v>
@@ -5006,16 +4970,16 @@
     </row>
     <row r="128" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A128" s="1" t="s">
-        <v>229</v>
+        <v>404</v>
       </c>
       <c r="B128" s="1" t="s">
-        <v>230</v>
+        <v>171</v>
       </c>
       <c r="C128" s="1" t="s">
-        <v>231</v>
+        <v>405</v>
       </c>
       <c r="D128" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E128" s="1">
         <v>2</v>
@@ -5023,16 +4987,16 @@
     </row>
     <row r="129" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A129" s="1" t="s">
-        <v>433</v>
+        <v>306</v>
       </c>
       <c r="B129" s="1" t="s">
-        <v>434</v>
+        <v>307</v>
       </c>
       <c r="C129" s="1" t="s">
-        <v>435</v>
+        <v>308</v>
       </c>
       <c r="D129" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E129" s="1">
         <v>2</v>
@@ -5040,16 +5004,16 @@
     </row>
     <row r="130" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A130" s="1" t="s">
-        <v>297</v>
+        <v>229</v>
       </c>
       <c r="B130" s="1" t="s">
-        <v>298</v>
+        <v>230</v>
       </c>
       <c r="C130" s="1" t="s">
-        <v>299</v>
+        <v>231</v>
       </c>
       <c r="D130" s="1">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E130" s="1">
         <v>2</v>
@@ -5057,13 +5021,13 @@
     </row>
     <row r="131" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A131" s="1" t="s">
-        <v>413</v>
+        <v>451</v>
       </c>
       <c r="B131" s="1" t="s">
-        <v>177</v>
+        <v>452</v>
       </c>
       <c r="C131" s="1" t="s">
-        <v>414</v>
+        <v>453</v>
       </c>
       <c r="D131" s="1">
         <v>1</v>
@@ -5074,13 +5038,13 @@
     </row>
     <row r="132" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A132" s="1" t="s">
-        <v>312</v>
+        <v>288</v>
       </c>
       <c r="B132" s="1" t="s">
-        <v>313</v>
+        <v>289</v>
       </c>
       <c r="C132" s="1" t="s">
-        <v>314</v>
+        <v>290</v>
       </c>
       <c r="D132" s="1">
         <v>1</v>
@@ -5091,16 +5055,16 @@
     </row>
     <row r="133" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A133" s="1" t="s">
-        <v>235</v>
+        <v>241</v>
       </c>
       <c r="B133" s="1" t="s">
-        <v>236</v>
+        <v>242</v>
       </c>
       <c r="C133" s="1" t="s">
-        <v>237</v>
+        <v>243</v>
       </c>
       <c r="D133" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E133" s="1">
         <v>2</v>
@@ -5108,13 +5072,13 @@
     </row>
     <row r="134" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A134" s="1" t="s">
-        <v>460</v>
+        <v>339</v>
       </c>
       <c r="B134" s="1" t="s">
-        <v>461</v>
+        <v>340</v>
       </c>
       <c r="C134" s="1" t="s">
-        <v>462</v>
+        <v>341</v>
       </c>
       <c r="D134" s="1">
         <v>1</v>
@@ -5125,16 +5089,16 @@
     </row>
     <row r="135" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A135" s="1" t="s">
-        <v>294</v>
+        <v>427</v>
       </c>
       <c r="B135" s="1" t="s">
-        <v>295</v>
+        <v>428</v>
       </c>
       <c r="C135" s="1" t="s">
-        <v>296</v>
+        <v>429</v>
       </c>
       <c r="D135" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E135" s="1">
         <v>2</v>
@@ -5142,16 +5106,16 @@
     </row>
     <row r="136" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A136" s="1" t="s">
-        <v>247</v>
+        <v>318</v>
       </c>
       <c r="B136" s="1" t="s">
-        <v>248</v>
+        <v>319</v>
       </c>
       <c r="C136" s="1" t="s">
-        <v>249</v>
+        <v>320</v>
       </c>
       <c r="D136" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E136" s="1">
         <v>2</v>
@@ -5159,13 +5123,13 @@
     </row>
     <row r="137" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A137" s="1" t="s">
-        <v>348</v>
+        <v>321</v>
       </c>
       <c r="B137" s="1" t="s">
-        <v>349</v>
+        <v>322</v>
       </c>
       <c r="C137" s="1" t="s">
-        <v>350</v>
+        <v>323</v>
       </c>
       <c r="D137" s="1">
         <v>1</v>
@@ -5176,13 +5140,13 @@
     </row>
     <row r="138" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A138" s="1" t="s">
-        <v>436</v>
+        <v>409</v>
       </c>
       <c r="B138" s="1" t="s">
-        <v>437</v>
+        <v>410</v>
       </c>
       <c r="C138" s="1" t="s">
-        <v>438</v>
+        <v>411</v>
       </c>
       <c r="D138" s="1">
         <v>0</v>
@@ -5193,16 +5157,16 @@
     </row>
     <row r="139" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A139" s="1" t="s">
-        <v>324</v>
+        <v>253</v>
       </c>
       <c r="B139" s="1" t="s">
-        <v>325</v>
+        <v>254</v>
       </c>
       <c r="C139" s="1" t="s">
-        <v>326</v>
+        <v>255</v>
       </c>
       <c r="D139" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E139" s="1">
         <v>2</v>
@@ -5210,13 +5174,13 @@
     </row>
     <row r="140" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A140" s="1" t="s">
-        <v>327</v>
+        <v>348</v>
       </c>
       <c r="B140" s="1" t="s">
-        <v>328</v>
+        <v>349</v>
       </c>
       <c r="C140" s="1" t="s">
-        <v>329</v>
+        <v>350</v>
       </c>
       <c r="D140" s="1">
         <v>1</v>
@@ -5227,16 +5191,16 @@
     </row>
     <row r="141" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A141" s="1" t="s">
-        <v>418</v>
+        <v>264</v>
       </c>
       <c r="B141" s="1" t="s">
-        <v>419</v>
+        <v>265</v>
       </c>
       <c r="C141" s="1" t="s">
-        <v>420</v>
+        <v>266</v>
       </c>
       <c r="D141" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E141" s="1">
         <v>2</v>
@@ -5244,13 +5208,13 @@
     </row>
     <row r="142" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A142" s="1" t="s">
-        <v>259</v>
+        <v>360</v>
       </c>
       <c r="B142" s="1" t="s">
-        <v>260</v>
+        <v>361</v>
       </c>
       <c r="C142" s="1" t="s">
-        <v>261</v>
+        <v>362</v>
       </c>
       <c r="D142" s="1">
         <v>2</v>
@@ -5261,13 +5225,13 @@
     </row>
     <row r="143" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A143" s="1" t="s">
-        <v>357</v>
+        <v>315</v>
       </c>
       <c r="B143" s="1" t="s">
-        <v>358</v>
+        <v>316</v>
       </c>
       <c r="C143" s="1" t="s">
-        <v>359</v>
+        <v>317</v>
       </c>
       <c r="D143" s="1">
         <v>1</v>
@@ -5278,13 +5242,13 @@
     </row>
     <row r="144" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A144" s="1" t="s">
-        <v>270</v>
+        <v>395</v>
       </c>
       <c r="B144" s="1" t="s">
-        <v>271</v>
+        <v>396</v>
       </c>
       <c r="C144" s="1" t="s">
-        <v>272</v>
+        <v>397</v>
       </c>
       <c r="D144" s="1">
         <v>2</v>
@@ -5295,16 +5259,16 @@
     </row>
     <row r="145" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A145" s="1" t="s">
-        <v>369</v>
+        <v>309</v>
       </c>
       <c r="B145" s="1" t="s">
-        <v>370</v>
+        <v>310</v>
       </c>
       <c r="C145" s="1" t="s">
-        <v>371</v>
+        <v>311</v>
       </c>
       <c r="D145" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E145" s="1">
         <v>2</v>
@@ -5312,13 +5276,13 @@
     </row>
     <row r="146" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A146" s="1" t="s">
-        <v>321</v>
+        <v>401</v>
       </c>
       <c r="B146" s="1" t="s">
-        <v>322</v>
+        <v>402</v>
       </c>
       <c r="C146" s="1" t="s">
-        <v>323</v>
+        <v>403</v>
       </c>
       <c r="D146" s="1">
         <v>1</v>
@@ -5329,16 +5293,16 @@
     </row>
     <row r="147" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A147" s="1" t="s">
-        <v>404</v>
+        <v>336</v>
       </c>
       <c r="B147" s="1" t="s">
-        <v>405</v>
+        <v>337</v>
       </c>
       <c r="C147" s="1" t="s">
-        <v>406</v>
+        <v>338</v>
       </c>
       <c r="D147" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E147" s="1">
         <v>2</v>
@@ -5346,13 +5310,13 @@
     </row>
     <row r="148" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A148" s="1" t="s">
-        <v>315</v>
+        <v>282</v>
       </c>
       <c r="B148" s="1" t="s">
-        <v>316</v>
+        <v>283</v>
       </c>
       <c r="C148" s="1" t="s">
-        <v>317</v>
+        <v>284</v>
       </c>
       <c r="D148" s="1">
         <v>1</v>
@@ -5363,16 +5327,16 @@
     </row>
     <row r="149" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A149" s="1" t="s">
-        <v>410</v>
+        <v>259</v>
       </c>
       <c r="B149" s="1" t="s">
-        <v>411</v>
+        <v>260</v>
       </c>
       <c r="C149" s="1" t="s">
-        <v>412</v>
+        <v>261</v>
       </c>
       <c r="D149" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E149" s="1">
         <v>2</v>
@@ -5380,16 +5344,16 @@
     </row>
     <row r="150" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A150" s="1" t="s">
-        <v>345</v>
+        <v>256</v>
       </c>
       <c r="B150" s="1" t="s">
-        <v>346</v>
+        <v>257</v>
       </c>
       <c r="C150" s="1" t="s">
-        <v>347</v>
+        <v>258</v>
       </c>
       <c r="D150" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E150" s="1">
         <v>2</v>
@@ -5397,16 +5361,16 @@
     </row>
     <row r="151" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A151" s="1" t="s">
-        <v>288</v>
+        <v>211</v>
       </c>
       <c r="B151" s="1" t="s">
-        <v>289</v>
+        <v>212</v>
       </c>
       <c r="C151" s="1" t="s">
-        <v>290</v>
+        <v>213</v>
       </c>
       <c r="D151" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E151" s="1">
         <v>2</v>
@@ -5414,16 +5378,16 @@
     </row>
     <row r="152" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A152" s="1" t="s">
-        <v>265</v>
+        <v>357</v>
       </c>
       <c r="B152" s="1" t="s">
-        <v>266</v>
+        <v>358</v>
       </c>
       <c r="C152" s="1" t="s">
-        <v>267</v>
+        <v>359</v>
       </c>
       <c r="D152" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E152" s="1">
         <v>2</v>
@@ -5431,16 +5395,16 @@
     </row>
     <row r="153" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A153" s="1" t="s">
-        <v>262</v>
+        <v>351</v>
       </c>
       <c r="B153" s="1" t="s">
-        <v>263</v>
+        <v>352</v>
       </c>
       <c r="C153" s="1" t="s">
-        <v>264</v>
+        <v>353</v>
       </c>
       <c r="D153" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E153" s="1">
         <v>2</v>
@@ -5448,16 +5412,16 @@
     </row>
     <row r="154" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A154" s="1" t="s">
-        <v>217</v>
+        <v>333</v>
       </c>
       <c r="B154" s="1" t="s">
-        <v>218</v>
+        <v>334</v>
       </c>
       <c r="C154" s="1" t="s">
-        <v>219</v>
+        <v>335</v>
       </c>
       <c r="D154" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E154" s="1">
         <v>2</v>
@@ -5465,16 +5429,16 @@
     </row>
     <row r="155" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A155" s="1" t="s">
-        <v>366</v>
+        <v>262</v>
       </c>
       <c r="B155" s="1" t="s">
-        <v>367</v>
+        <v>263</v>
       </c>
       <c r="C155" s="1" t="s">
-        <v>368</v>
+        <v>261</v>
       </c>
       <c r="D155" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E155" s="1">
         <v>2</v>
@@ -5482,16 +5446,16 @@
     </row>
     <row r="156" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A156" s="1" t="s">
-        <v>360</v>
+        <v>389</v>
       </c>
       <c r="B156" s="1" t="s">
-        <v>361</v>
+        <v>390</v>
       </c>
       <c r="C156" s="1" t="s">
-        <v>362</v>
+        <v>391</v>
       </c>
       <c r="D156" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E156" s="1">
         <v>2</v>
@@ -5499,16 +5463,16 @@
     </row>
     <row r="157" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A157" s="1" t="s">
-        <v>342</v>
+        <v>381</v>
       </c>
       <c r="B157" s="1" t="s">
-        <v>343</v>
+        <v>382</v>
       </c>
       <c r="C157" s="1" t="s">
-        <v>344</v>
+        <v>383</v>
       </c>
       <c r="D157" s="1">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E157" s="1">
         <v>2</v>
@@ -5516,16 +5480,16 @@
     </row>
     <row r="158" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A158" s="1" t="s">
-        <v>268</v>
+        <v>345</v>
       </c>
       <c r="B158" s="1" t="s">
-        <v>269</v>
+        <v>346</v>
       </c>
       <c r="C158" s="1" t="s">
-        <v>267</v>
+        <v>347</v>
       </c>
       <c r="D158" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E158" s="1">
         <v>2</v>
@@ -5533,67 +5497,67 @@
     </row>
     <row r="159" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A159" s="1" t="s">
-        <v>398</v>
+        <v>504</v>
       </c>
       <c r="B159" s="1" t="s">
-        <v>399</v>
+        <v>505</v>
       </c>
       <c r="C159" s="1" t="s">
-        <v>400</v>
+        <v>506</v>
       </c>
       <c r="D159" s="1">
         <v>2</v>
       </c>
       <c r="E159" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="160" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A160" s="1" t="s">
-        <v>390</v>
+        <v>498</v>
       </c>
       <c r="B160" s="1" t="s">
-        <v>391</v>
+        <v>499</v>
       </c>
       <c r="C160" s="1" t="s">
-        <v>392</v>
+        <v>500</v>
       </c>
       <c r="D160" s="1">
+        <v>1</v>
+      </c>
+      <c r="E160" s="1">
         <v>3</v>
-      </c>
-      <c r="E160" s="1">
-        <v>2</v>
       </c>
     </row>
     <row r="161" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A161" s="1" t="s">
-        <v>354</v>
+        <v>501</v>
       </c>
       <c r="B161" s="1" t="s">
-        <v>355</v>
+        <v>502</v>
       </c>
       <c r="C161" s="1" t="s">
-        <v>356</v>
+        <v>503</v>
       </c>
       <c r="D161" s="1">
         <v>1</v>
       </c>
       <c r="E161" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="162" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A162" s="1" t="s">
-        <v>513</v>
+        <v>540</v>
       </c>
       <c r="B162" s="1" t="s">
-        <v>514</v>
+        <v>541</v>
       </c>
       <c r="C162" s="1" t="s">
-        <v>515</v>
+        <v>542</v>
       </c>
       <c r="D162" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E162" s="1">
         <v>3</v>
@@ -5601,13 +5565,13 @@
     </row>
     <row r="163" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A163" s="1" t="s">
-        <v>507</v>
+        <v>537</v>
       </c>
       <c r="B163" s="1" t="s">
-        <v>508</v>
+        <v>538</v>
       </c>
       <c r="C163" s="1" t="s">
-        <v>509</v>
+        <v>539</v>
       </c>
       <c r="D163" s="1">
         <v>1</v>
@@ -5618,13 +5582,13 @@
     </row>
     <row r="164" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A164" s="1" t="s">
-        <v>510</v>
+        <v>543</v>
       </c>
       <c r="B164" s="1" t="s">
-        <v>511</v>
+        <v>544</v>
       </c>
       <c r="C164" s="1" t="s">
-        <v>512</v>
+        <v>545</v>
       </c>
       <c r="D164" s="1">
         <v>1</v>
@@ -5635,13 +5599,13 @@
     </row>
     <row r="165" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A165" s="1" t="s">
-        <v>552</v>
+        <v>525</v>
       </c>
       <c r="B165" s="1" t="s">
-        <v>553</v>
+        <v>526</v>
       </c>
       <c r="C165" s="1" t="s">
-        <v>554</v>
+        <v>527</v>
       </c>
       <c r="D165" s="1">
         <v>1</v>
@@ -5652,16 +5616,16 @@
     </row>
     <row r="166" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A166" s="1" t="s">
-        <v>549</v>
+        <v>507</v>
       </c>
       <c r="B166" s="1" t="s">
-        <v>550</v>
+        <v>508</v>
       </c>
       <c r="C166" s="1" t="s">
-        <v>551</v>
+        <v>509</v>
       </c>
       <c r="D166" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E166" s="1">
         <v>3</v>
@@ -5669,16 +5633,16 @@
     </row>
     <row r="167" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A167" s="1" t="s">
-        <v>555</v>
+        <v>489</v>
       </c>
       <c r="B167" s="1" t="s">
-        <v>556</v>
+        <v>490</v>
       </c>
       <c r="C167" s="1" t="s">
-        <v>557</v>
+        <v>491</v>
       </c>
       <c r="D167" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E167" s="1">
         <v>3</v>
@@ -5686,13 +5650,13 @@
     </row>
     <row r="168" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A168" s="1" t="s">
-        <v>537</v>
+        <v>483</v>
       </c>
       <c r="B168" s="1" t="s">
-        <v>538</v>
+        <v>484</v>
       </c>
       <c r="C168" s="1" t="s">
-        <v>539</v>
+        <v>485</v>
       </c>
       <c r="D168" s="1">
         <v>1</v>
@@ -5703,13 +5667,13 @@
     </row>
     <row r="169" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A169" s="1" t="s">
-        <v>516</v>
+        <v>492</v>
       </c>
       <c r="B169" s="1" t="s">
-        <v>517</v>
+        <v>493</v>
       </c>
       <c r="C169" s="1" t="s">
-        <v>518</v>
+        <v>494</v>
       </c>
       <c r="D169" s="1">
         <v>2</v>
@@ -5720,16 +5684,16 @@
     </row>
     <row r="170" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A170" s="1" t="s">
-        <v>498</v>
+        <v>516</v>
       </c>
       <c r="B170" s="1" t="s">
-        <v>499</v>
+        <v>517</v>
       </c>
       <c r="C170" s="1" t="s">
-        <v>500</v>
+        <v>518</v>
       </c>
       <c r="D170" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E170" s="1">
         <v>3</v>
@@ -5737,16 +5701,16 @@
     </row>
     <row r="171" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A171" s="1" t="s">
-        <v>492</v>
+        <v>495</v>
       </c>
       <c r="B171" s="1" t="s">
-        <v>493</v>
+        <v>496</v>
       </c>
       <c r="C171" s="1" t="s">
-        <v>494</v>
+        <v>497</v>
       </c>
       <c r="D171" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E171" s="1">
         <v>3</v>
@@ -5754,13 +5718,13 @@
     </row>
     <row r="172" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A172" s="1" t="s">
-        <v>501</v>
+        <v>469</v>
       </c>
       <c r="B172" s="1" t="s">
-        <v>502</v>
+        <v>470</v>
       </c>
       <c r="C172" s="1" t="s">
-        <v>503</v>
+        <v>471</v>
       </c>
       <c r="D172" s="1">
         <v>2</v>
@@ -5771,16 +5735,16 @@
     </row>
     <row r="173" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A173" s="1" t="s">
-        <v>525</v>
+        <v>481</v>
       </c>
       <c r="B173" s="1" t="s">
-        <v>526</v>
+        <v>295</v>
       </c>
       <c r="C173" s="1" t="s">
-        <v>527</v>
+        <v>482</v>
       </c>
       <c r="D173" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E173" s="1">
         <v>3</v>
@@ -5788,16 +5752,16 @@
     </row>
     <row r="174" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A174" s="1" t="s">
-        <v>504</v>
+        <v>549</v>
       </c>
       <c r="B174" s="1" t="s">
-        <v>505</v>
+        <v>550</v>
       </c>
       <c r="C174" s="1" t="s">
-        <v>506</v>
+        <v>551</v>
       </c>
       <c r="D174" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E174" s="1">
         <v>3</v>
@@ -5805,13 +5769,13 @@
     </row>
     <row r="175" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A175" s="1" t="s">
-        <v>478</v>
+        <v>472</v>
       </c>
       <c r="B175" s="1" t="s">
-        <v>479</v>
+        <v>473</v>
       </c>
       <c r="C175" s="1" t="s">
-        <v>480</v>
+        <v>474</v>
       </c>
       <c r="D175" s="1">
         <v>2</v>
@@ -5822,13 +5786,13 @@
     </row>
     <row r="176" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A176" s="1" t="s">
-        <v>490</v>
+        <v>478</v>
       </c>
       <c r="B176" s="1" t="s">
-        <v>301</v>
+        <v>479</v>
       </c>
       <c r="C176" s="1" t="s">
-        <v>491</v>
+        <v>480</v>
       </c>
       <c r="D176" s="1">
         <v>2</v>
@@ -5839,16 +5803,16 @@
     </row>
     <row r="177" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A177" s="1" t="s">
-        <v>561</v>
+        <v>522</v>
       </c>
       <c r="B177" s="1" t="s">
-        <v>562</v>
+        <v>523</v>
       </c>
       <c r="C177" s="1" t="s">
-        <v>563</v>
+        <v>524</v>
       </c>
       <c r="D177" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E177" s="1">
         <v>3</v>
@@ -5856,16 +5820,16 @@
     </row>
     <row r="178" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A178" s="1" t="s">
-        <v>481</v>
+        <v>546</v>
       </c>
       <c r="B178" s="1" t="s">
-        <v>482</v>
+        <v>547</v>
       </c>
       <c r="C178" s="1" t="s">
-        <v>483</v>
+        <v>548</v>
       </c>
       <c r="D178" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E178" s="1">
         <v>3</v>
@@ -5873,13 +5837,13 @@
     </row>
     <row r="179" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A179" s="1" t="s">
-        <v>487</v>
+        <v>519</v>
       </c>
       <c r="B179" s="1" t="s">
-        <v>488</v>
+        <v>520</v>
       </c>
       <c r="C179" s="1" t="s">
-        <v>489</v>
+        <v>521</v>
       </c>
       <c r="D179" s="1">
         <v>2</v>
@@ -5890,16 +5854,16 @@
     </row>
     <row r="180" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A180" s="1" t="s">
-        <v>531</v>
+        <v>534</v>
       </c>
       <c r="B180" s="1" t="s">
-        <v>532</v>
+        <v>535</v>
       </c>
       <c r="C180" s="1" t="s">
-        <v>533</v>
+        <v>536</v>
       </c>
       <c r="D180" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E180" s="1">
         <v>3</v>
@@ -5907,13 +5871,13 @@
     </row>
     <row r="181" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A181" s="1" t="s">
-        <v>558</v>
+        <v>528</v>
       </c>
       <c r="B181" s="1" t="s">
-        <v>559</v>
+        <v>529</v>
       </c>
       <c r="C181" s="1" t="s">
-        <v>560</v>
+        <v>530</v>
       </c>
       <c r="D181" s="1">
         <v>1</v>
@@ -5924,16 +5888,16 @@
     </row>
     <row r="182" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A182" s="1" t="s">
-        <v>528</v>
+        <v>486</v>
       </c>
       <c r="B182" s="1" t="s">
-        <v>529</v>
+        <v>487</v>
       </c>
       <c r="C182" s="1" t="s">
-        <v>530</v>
+        <v>488</v>
       </c>
       <c r="D182" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E182" s="1">
         <v>3</v>
@@ -5941,16 +5905,16 @@
     </row>
     <row r="183" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A183" s="1" t="s">
-        <v>546</v>
+        <v>510</v>
       </c>
       <c r="B183" s="1" t="s">
-        <v>547</v>
+        <v>511</v>
       </c>
       <c r="C183" s="1" t="s">
-        <v>548</v>
+        <v>512</v>
       </c>
       <c r="D183" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E183" s="1">
         <v>3</v>
@@ -5958,13 +5922,13 @@
     </row>
     <row r="184" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A184" s="1" t="s">
-        <v>540</v>
+        <v>531</v>
       </c>
       <c r="B184" s="1" t="s">
-        <v>541</v>
+        <v>532</v>
       </c>
       <c r="C184" s="1" t="s">
-        <v>542</v>
+        <v>533</v>
       </c>
       <c r="D184" s="1">
         <v>1</v>
@@ -5975,16 +5939,16 @@
     </row>
     <row r="185" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A185" s="1" t="s">
-        <v>534</v>
+        <v>475</v>
       </c>
       <c r="B185" s="1" t="s">
-        <v>535</v>
+        <v>476</v>
       </c>
       <c r="C185" s="1" t="s">
-        <v>536</v>
+        <v>477</v>
       </c>
       <c r="D185" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E185" s="1">
         <v>3</v>
@@ -5992,13 +5956,13 @@
     </row>
     <row r="186" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A186" s="1" t="s">
-        <v>495</v>
+        <v>513</v>
       </c>
       <c r="B186" s="1" t="s">
-        <v>496</v>
+        <v>514</v>
       </c>
       <c r="C186" s="1" t="s">
-        <v>497</v>
+        <v>515</v>
       </c>
       <c r="D186" s="1">
         <v>1</v>
@@ -6009,16 +5973,16 @@
     </row>
     <row r="187" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A187" s="1" t="s">
-        <v>519</v>
+        <v>552</v>
       </c>
       <c r="B187" s="1" t="s">
-        <v>520</v>
+        <v>553</v>
       </c>
       <c r="C187" s="1" t="s">
-        <v>521</v>
+        <v>554</v>
       </c>
       <c r="D187" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E187" s="1">
         <v>3</v>
@@ -6026,81 +5990,81 @@
     </row>
     <row r="188" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A188" s="1" t="s">
-        <v>543</v>
+        <v>570</v>
       </c>
       <c r="B188" s="1" t="s">
-        <v>544</v>
+        <v>571</v>
       </c>
       <c r="C188" s="1" t="s">
-        <v>545</v>
+        <v>572</v>
       </c>
       <c r="D188" s="1">
         <v>1</v>
       </c>
       <c r="E188" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="189" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A189" s="1" t="s">
-        <v>484</v>
+        <v>558</v>
       </c>
       <c r="B189" s="1" t="s">
-        <v>485</v>
+        <v>559</v>
       </c>
       <c r="C189" s="1" t="s">
-        <v>486</v>
+        <v>560</v>
       </c>
       <c r="D189" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E189" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="190" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A190" s="1" t="s">
-        <v>522</v>
+        <v>567</v>
       </c>
       <c r="B190" s="1" t="s">
-        <v>523</v>
+        <v>568</v>
       </c>
       <c r="C190" s="1" t="s">
-        <v>524</v>
+        <v>569</v>
       </c>
       <c r="D190" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E190" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="191" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A191" s="1" t="s">
-        <v>564</v>
+        <v>561</v>
       </c>
       <c r="B191" s="1" t="s">
-        <v>565</v>
+        <v>562</v>
       </c>
       <c r="C191" s="1" t="s">
-        <v>566</v>
+        <v>563</v>
       </c>
       <c r="D191" s="1">
         <v>1</v>
       </c>
       <c r="E191" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="192" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A192" s="1" t="s">
-        <v>582</v>
+        <v>564</v>
       </c>
       <c r="B192" s="1" t="s">
-        <v>583</v>
+        <v>565</v>
       </c>
       <c r="C192" s="1" t="s">
-        <v>584</v>
+        <v>566</v>
       </c>
       <c r="D192" s="1">
         <v>1</v>
@@ -6111,16 +6075,16 @@
     </row>
     <row r="193" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A193" s="1" t="s">
-        <v>570</v>
+        <v>582</v>
       </c>
       <c r="B193" s="1" t="s">
-        <v>571</v>
+        <v>583</v>
       </c>
       <c r="C193" s="1" t="s">
-        <v>572</v>
+        <v>584</v>
       </c>
       <c r="D193" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E193" s="1">
         <v>4</v>
@@ -6145,16 +6109,16 @@
     </row>
     <row r="195" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A195" s="1" t="s">
-        <v>573</v>
+        <v>591</v>
       </c>
       <c r="B195" s="1" t="s">
-        <v>574</v>
+        <v>592</v>
       </c>
       <c r="C195" s="1" t="s">
-        <v>575</v>
+        <v>593</v>
       </c>
       <c r="D195" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E195" s="1">
         <v>4</v>
@@ -6162,13 +6126,13 @@
     </row>
     <row r="196" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A196" s="1" t="s">
-        <v>576</v>
+        <v>588</v>
       </c>
       <c r="B196" s="1" t="s">
-        <v>577</v>
+        <v>589</v>
       </c>
       <c r="C196" s="1" t="s">
-        <v>578</v>
+        <v>590</v>
       </c>
       <c r="D196" s="1">
         <v>1</v>
@@ -6179,16 +6143,16 @@
     </row>
     <row r="197" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A197" s="1" t="s">
-        <v>594</v>
+        <v>576</v>
       </c>
       <c r="B197" s="1" t="s">
-        <v>595</v>
+        <v>577</v>
       </c>
       <c r="C197" s="1" t="s">
-        <v>596</v>
+        <v>578</v>
       </c>
       <c r="D197" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E197" s="1">
         <v>4</v>
@@ -6196,16 +6160,16 @@
     </row>
     <row r="198" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A198" s="1" t="s">
-        <v>591</v>
+        <v>573</v>
       </c>
       <c r="B198" s="1" t="s">
-        <v>592</v>
+        <v>574</v>
       </c>
       <c r="C198" s="1" t="s">
-        <v>593</v>
+        <v>575</v>
       </c>
       <c r="D198" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E198" s="1">
         <v>4</v>
@@ -6213,13 +6177,13 @@
     </row>
     <row r="199" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A199" s="1" t="s">
-        <v>603</v>
+        <v>585</v>
       </c>
       <c r="B199" s="1" t="s">
-        <v>604</v>
+        <v>586</v>
       </c>
       <c r="C199" s="1" t="s">
-        <v>605</v>
+        <v>587</v>
       </c>
       <c r="D199" s="1">
         <v>0</v>
@@ -6230,16 +6194,16 @@
     </row>
     <row r="200" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A200" s="1" t="s">
-        <v>600</v>
+        <v>555</v>
       </c>
       <c r="B200" s="1" t="s">
-        <v>601</v>
+        <v>556</v>
       </c>
       <c r="C200" s="1" t="s">
-        <v>602</v>
+        <v>557</v>
       </c>
       <c r="D200" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E200" s="1">
         <v>4</v>
@@ -6247,179 +6211,111 @@
     </row>
     <row r="201" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A201" s="1" t="s">
-        <v>588</v>
+        <v>594</v>
       </c>
       <c r="B201" s="1" t="s">
-        <v>589</v>
+        <v>595</v>
       </c>
       <c r="C201" s="1" t="s">
-        <v>590</v>
+        <v>596</v>
       </c>
       <c r="D201" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E201" s="1">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="202" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A202" s="1" t="s">
-        <v>585</v>
+        <v>599</v>
       </c>
       <c r="B202" s="1" t="s">
-        <v>586</v>
+        <v>600</v>
       </c>
       <c r="C202" s="1" t="s">
-        <v>587</v>
+        <v>601</v>
       </c>
       <c r="D202" s="1">
         <v>1</v>
       </c>
       <c r="E202" s="1">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="203" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A203" s="1" t="s">
-        <v>597</v>
+        <v>602</v>
       </c>
       <c r="B203" s="1" t="s">
-        <v>598</v>
+        <v>603</v>
       </c>
       <c r="C203" s="1" t="s">
-        <v>599</v>
+        <v>604</v>
       </c>
       <c r="D203" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E203" s="1">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="204" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A204" s="1" t="s">
-        <v>567</v>
+        <v>597</v>
       </c>
       <c r="B204" s="1" t="s">
-        <v>568</v>
+        <v>514</v>
       </c>
       <c r="C204" s="1" t="s">
-        <v>569</v>
+        <v>598</v>
       </c>
       <c r="D204" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E204" s="1">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="205" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A205" s="1" t="s">
+        <v>605</v>
+      </c>
+      <c r="B205" s="1" t="s">
         <v>606</v>
       </c>
-      <c r="B205" s="1" t="s">
+      <c r="C205" s="1" t="s">
         <v>607</v>
       </c>
-      <c r="C205" s="1" t="s">
-        <v>608</v>
-      </c>
       <c r="D205" s="1">
         <v>1</v>
       </c>
       <c r="E205" s="1">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="206" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A206" s="1" t="s">
-        <v>611</v>
+        <v>608</v>
       </c>
       <c r="B206" s="1" t="s">
-        <v>612</v>
+        <v>609</v>
       </c>
       <c r="C206" s="1" t="s">
-        <v>613</v>
+        <v>610</v>
       </c>
       <c r="D206" s="1">
         <v>1</v>
       </c>
       <c r="E206" s="1">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="207" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A207" s="1" t="s">
-        <v>614</v>
-      </c>
-      <c r="B207" s="1" t="s">
-        <v>615</v>
-      </c>
-      <c r="C207" s="1" t="s">
-        <v>616</v>
-      </c>
-      <c r="D207" s="1">
-        <v>2</v>
-      </c>
-      <c r="E207" s="1">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="208" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A208" s="1" t="s">
-        <v>609</v>
-      </c>
-      <c r="B208" s="1" t="s">
-        <v>523</v>
-      </c>
-      <c r="C208" s="1" t="s">
-        <v>610</v>
-      </c>
-      <c r="D208" s="1">
-        <v>2</v>
-      </c>
-      <c r="E208" s="1">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="209" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A209" s="1" t="s">
-        <v>617</v>
-      </c>
-      <c r="B209" s="1" t="s">
-        <v>618</v>
-      </c>
-      <c r="C209" s="1" t="s">
-        <v>619</v>
-      </c>
-      <c r="D209" s="1">
-        <v>1</v>
-      </c>
-      <c r="E209" s="1">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="210" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A210" s="1" t="s">
-        <v>620</v>
-      </c>
-      <c r="B210" s="1" t="s">
-        <v>621</v>
-      </c>
-      <c r="C210" s="1" t="s">
-        <v>622</v>
-      </c>
-      <c r="D210" s="1">
-        <v>1</v>
-      </c>
-      <c r="E210" s="1">
         <v>7</v>
       </c>
     </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A3:E210">
-    <sortCondition ref="E3:E210"/>
-    <sortCondition ref="A3:A210"/>
-    <sortCondition ref="D3:D210"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A3:E206">
+    <sortCondition ref="E3:E206"/>
+    <sortCondition ref="A3:A206"/>
+    <sortCondition ref="D3:D206"/>
   </sortState>
   <phoneticPr fontId="18" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/dev_stuffs/4匠魂词条.csv.xlsx
+++ b/dev_stuffs/4匠魂词条.csv.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Tony\Documents\EX\HMCL\.minecraft\versions\Palmon\dev_stuffs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5779ACC2-4C98-4651-802B-859BF8329F36}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B80F4992-C554-45EF-A62D-B8F82A18C034}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21240" xr2:uid="{982397F0-7A37-43D3-9AE4-F623F1211744}"/>
+    <workbookView xWindow="5355" yWindow="3375" windowWidth="24015" windowHeight="15435" xr2:uid="{982397F0-7A37-43D3-9AE4-F623F1211744}"/>
   </bookViews>
   <sheets>
     <sheet name="4匠魂词条" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="617" uniqueCount="611">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="614" uniqueCount="608">
   <si>
     <t>通用：0，工具：1，防御：2，远程：3</t>
   </si>
@@ -80,15 +80,6 @@
   </si>
   <si>
     <t>这个工具上的黏液覆层可以变得很厚</t>
-  </si>
-  <si>
-    <t>tcintegrations:roadrunner</t>
-  </si>
-  <si>
-    <t>走鹃</t>
-  </si>
-  <si>
-    <t>增加在沙子上的移动速度。</t>
   </si>
   <si>
     <t>tconstruct:trueshot</t>
@@ -2815,7 +2806,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{66160D17-E746-45B6-B9FC-167F4F38C3EE}">
-  <dimension ref="A1:E206"/>
+  <dimension ref="A1:E205"/>
   <sheetFormatPr defaultRowHeight="18" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="37.5" style="1" customWidth="1"/>
@@ -2848,13 +2839,13 @@
     </row>
     <row r="3" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="1" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="D3" s="1">
         <v>1</v>
@@ -2899,13 +2890,13 @@
     </row>
     <row r="6" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="1" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="D6" s="1">
         <v>1</v>
@@ -2916,13 +2907,13 @@
     </row>
     <row r="7" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="1" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>190</v>
+        <v>187</v>
       </c>
       <c r="D7" s="1">
         <v>1</v>
@@ -2933,13 +2924,13 @@
     </row>
     <row r="8" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="1" t="s">
-        <v>205</v>
+        <v>202</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>206</v>
+        <v>203</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="D8" s="1">
         <v>0</v>
@@ -2950,13 +2941,13 @@
     </row>
     <row r="9" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="1" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="D9" s="1">
         <v>1</v>
@@ -2967,13 +2958,13 @@
     </row>
     <row r="10" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="1" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="D10" s="1">
         <v>1</v>
@@ -2984,16 +2975,16 @@
     </row>
     <row r="11" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="1" t="s">
-        <v>20</v>
+        <v>41</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>21</v>
+        <v>42</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>22</v>
+        <v>43</v>
       </c>
       <c r="D11" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E11" s="1">
         <v>1</v>
@@ -3001,13 +2992,13 @@
     </row>
     <row r="12" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="1" t="s">
-        <v>44</v>
+        <v>6</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>45</v>
+        <v>7</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>46</v>
+        <v>8</v>
       </c>
       <c r="D12" s="1">
         <v>1</v>
@@ -3018,16 +3009,16 @@
     </row>
     <row r="13" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="1" t="s">
-        <v>6</v>
+        <v>194</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>7</v>
+        <v>195</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>8</v>
+        <v>196</v>
       </c>
       <c r="D13" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E13" s="1">
         <v>1</v>
@@ -3035,16 +3026,16 @@
     </row>
     <row r="14" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="1" t="s">
-        <v>197</v>
+        <v>116</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>198</v>
+        <v>117</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>199</v>
+        <v>118</v>
       </c>
       <c r="D14" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E14" s="1">
         <v>1</v>
@@ -3052,16 +3043,16 @@
     </row>
     <row r="15" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="1" t="s">
-        <v>119</v>
+        <v>59</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>120</v>
+        <v>60</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>121</v>
+        <v>61</v>
       </c>
       <c r="D15" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E15" s="1">
         <v>1</v>
@@ -3069,16 +3060,16 @@
     </row>
     <row r="16" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="1" t="s">
-        <v>62</v>
+        <v>71</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>63</v>
+        <v>72</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>64</v>
+        <v>73</v>
       </c>
       <c r="D16" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E16" s="1">
         <v>1</v>
@@ -3086,13 +3077,13 @@
     </row>
     <row r="17" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="1" t="s">
-        <v>74</v>
+        <v>146</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>75</v>
+        <v>147</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>76</v>
+        <v>148</v>
       </c>
       <c r="D17" s="1">
         <v>1</v>
@@ -3103,16 +3094,16 @@
     </row>
     <row r="18" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A18" s="1" t="s">
-        <v>149</v>
+        <v>137</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>150</v>
+        <v>138</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>151</v>
+        <v>139</v>
       </c>
       <c r="D18" s="1">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E18" s="1">
         <v>1</v>
@@ -3120,16 +3111,16 @@
     </row>
     <row r="19" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="1" t="s">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="D19" s="1">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E19" s="1">
         <v>1</v>
@@ -3137,13 +3128,13 @@
     </row>
     <row r="20" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A20" s="1" t="s">
-        <v>146</v>
+        <v>161</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>147</v>
+        <v>162</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>148</v>
+        <v>163</v>
       </c>
       <c r="D20" s="1">
         <v>0</v>
@@ -3154,16 +3145,16 @@
     </row>
     <row r="21" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A21" s="1" t="s">
-        <v>164</v>
+        <v>77</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>165</v>
+        <v>78</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>166</v>
+        <v>79</v>
       </c>
       <c r="D21" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E21" s="1">
         <v>1</v>
@@ -3171,16 +3162,16 @@
     </row>
     <row r="22" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A22" s="1" t="s">
-        <v>80</v>
+        <v>95</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>81</v>
+        <v>96</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>82</v>
+        <v>97</v>
       </c>
       <c r="D22" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E22" s="1">
         <v>1</v>
@@ -3188,16 +3179,16 @@
     </row>
     <row r="23" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A23" s="1" t="s">
-        <v>98</v>
+        <v>80</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>99</v>
+        <v>81</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>100</v>
+        <v>82</v>
       </c>
       <c r="D23" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E23" s="1">
         <v>1</v>
@@ -3205,16 +3196,16 @@
     </row>
     <row r="24" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A24" s="1" t="s">
-        <v>83</v>
+        <v>53</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>84</v>
+        <v>54</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>85</v>
+        <v>55</v>
       </c>
       <c r="D24" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E24" s="1">
         <v>1</v>
@@ -3222,16 +3213,16 @@
     </row>
     <row r="25" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A25" s="1" t="s">
-        <v>56</v>
+        <v>35</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>57</v>
+        <v>36</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>58</v>
+        <v>37</v>
       </c>
       <c r="D25" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E25" s="1">
         <v>1</v>
@@ -3239,16 +3230,16 @@
     </row>
     <row r="26" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A26" s="1" t="s">
-        <v>38</v>
+        <v>47</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>39</v>
+        <v>48</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>40</v>
+        <v>49</v>
       </c>
       <c r="D26" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E26" s="1">
         <v>1</v>
@@ -3256,16 +3247,16 @@
     </row>
     <row r="27" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A27" s="1" t="s">
-        <v>50</v>
+        <v>68</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>51</v>
+        <v>69</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>52</v>
+        <v>70</v>
       </c>
       <c r="D27" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E27" s="1">
         <v>1</v>
@@ -3273,13 +3264,13 @@
     </row>
     <row r="28" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A28" s="1" t="s">
-        <v>71</v>
+        <v>134</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>72</v>
+        <v>135</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>73</v>
+        <v>136</v>
       </c>
       <c r="D28" s="1">
         <v>1</v>
@@ -3290,13 +3281,13 @@
     </row>
     <row r="29" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A29" s="1" t="s">
-        <v>137</v>
+        <v>197</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>138</v>
+        <v>186</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>139</v>
+        <v>198</v>
       </c>
       <c r="D29" s="1">
         <v>1</v>
@@ -3307,16 +3298,16 @@
     </row>
     <row r="30" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A30" s="1" t="s">
-        <v>200</v>
+        <v>56</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>189</v>
+        <v>57</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>201</v>
+        <v>58</v>
       </c>
       <c r="D30" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E30" s="1">
         <v>1</v>
@@ -3324,16 +3315,16 @@
     </row>
     <row r="31" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A31" s="1" t="s">
-        <v>59</v>
+        <v>199</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>60</v>
+        <v>200</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>61</v>
+        <v>201</v>
       </c>
       <c r="D31" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E31" s="1">
         <v>1</v>
@@ -3341,13 +3332,13 @@
     </row>
     <row r="32" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A32" s="1" t="s">
-        <v>202</v>
+        <v>104</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>203</v>
+        <v>105</v>
       </c>
       <c r="C32" s="1" t="s">
-        <v>204</v>
+        <v>106</v>
       </c>
       <c r="D32" s="1">
         <v>1</v>
@@ -3358,13 +3349,13 @@
     </row>
     <row r="33" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A33" s="1" t="s">
-        <v>107</v>
+        <v>179</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>108</v>
+        <v>180</v>
       </c>
       <c r="C33" s="1" t="s">
-        <v>109</v>
+        <v>181</v>
       </c>
       <c r="D33" s="1">
         <v>1</v>
@@ -3375,13 +3366,13 @@
     </row>
     <row r="34" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A34" s="1" t="s">
-        <v>182</v>
+        <v>101</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>183</v>
+        <v>102</v>
       </c>
       <c r="C34" s="1" t="s">
-        <v>184</v>
+        <v>103</v>
       </c>
       <c r="D34" s="1">
         <v>1</v>
@@ -3392,16 +3383,16 @@
     </row>
     <row r="35" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A35" s="1" t="s">
-        <v>104</v>
+        <v>158</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>105</v>
+        <v>159</v>
       </c>
       <c r="C35" s="1" t="s">
-        <v>106</v>
+        <v>160</v>
       </c>
       <c r="D35" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E35" s="1">
         <v>1</v>
@@ -3409,16 +3400,16 @@
     </row>
     <row r="36" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A36" s="1" t="s">
-        <v>161</v>
+        <v>50</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>162</v>
+        <v>51</v>
       </c>
       <c r="C36" s="1" t="s">
-        <v>163</v>
+        <v>52</v>
       </c>
       <c r="D36" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E36" s="1">
         <v>1</v>
@@ -3426,16 +3417,16 @@
     </row>
     <row r="37" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A37" s="1" t="s">
-        <v>53</v>
+        <v>86</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>54</v>
+        <v>87</v>
       </c>
       <c r="C37" s="1" t="s">
-        <v>55</v>
+        <v>88</v>
       </c>
       <c r="D37" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E37" s="1">
         <v>1</v>
@@ -3443,13 +3434,13 @@
     </row>
     <row r="38" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A38" s="1" t="s">
-        <v>89</v>
+        <v>128</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>90</v>
+        <v>129</v>
       </c>
       <c r="C38" s="1" t="s">
-        <v>91</v>
+        <v>130</v>
       </c>
       <c r="D38" s="1">
         <v>1</v>
@@ -3460,16 +3451,16 @@
     </row>
     <row r="39" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A39" s="1" t="s">
-        <v>131</v>
+        <v>17</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>132</v>
+        <v>18</v>
       </c>
       <c r="C39" s="1" t="s">
-        <v>133</v>
+        <v>19</v>
       </c>
       <c r="D39" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E39" s="1">
         <v>1</v>
@@ -3477,13 +3468,13 @@
     </row>
     <row r="40" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A40" s="1" t="s">
-        <v>17</v>
+        <v>44</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>18</v>
+        <v>45</v>
       </c>
       <c r="C40" s="1" t="s">
-        <v>19</v>
+        <v>46</v>
       </c>
       <c r="D40" s="1">
         <v>0</v>
@@ -3494,13 +3485,13 @@
     </row>
     <row r="41" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A41" s="1" t="s">
-        <v>47</v>
+        <v>170</v>
       </c>
       <c r="B41" s="1" t="s">
-        <v>48</v>
+        <v>171</v>
       </c>
       <c r="C41" s="1" t="s">
-        <v>49</v>
+        <v>172</v>
       </c>
       <c r="D41" s="1">
         <v>0</v>
@@ -3511,13 +3502,13 @@
     </row>
     <row r="42" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A42" s="1" t="s">
-        <v>173</v>
+        <v>23</v>
       </c>
       <c r="B42" s="1" t="s">
-        <v>174</v>
+        <v>24</v>
       </c>
       <c r="C42" s="1" t="s">
-        <v>175</v>
+        <v>25</v>
       </c>
       <c r="D42" s="1">
         <v>0</v>
@@ -3528,16 +3519,16 @@
     </row>
     <row r="43" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A43" s="1" t="s">
-        <v>26</v>
+        <v>131</v>
       </c>
       <c r="B43" s="1" t="s">
-        <v>27</v>
+        <v>132</v>
       </c>
       <c r="C43" s="1" t="s">
-        <v>28</v>
+        <v>133</v>
       </c>
       <c r="D43" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E43" s="1">
         <v>1</v>
@@ -3545,13 +3536,13 @@
     </row>
     <row r="44" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A44" s="1" t="s">
-        <v>134</v>
+        <v>167</v>
       </c>
       <c r="B44" s="1" t="s">
-        <v>135</v>
+        <v>168</v>
       </c>
       <c r="C44" s="1" t="s">
-        <v>136</v>
+        <v>169</v>
       </c>
       <c r="D44" s="1">
         <v>1</v>
@@ -3562,16 +3553,16 @@
     </row>
     <row r="45" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A45" s="1" t="s">
-        <v>170</v>
+        <v>191</v>
       </c>
       <c r="B45" s="1" t="s">
-        <v>171</v>
+        <v>192</v>
       </c>
       <c r="C45" s="1" t="s">
-        <v>172</v>
+        <v>193</v>
       </c>
       <c r="D45" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E45" s="1">
         <v>1</v>
@@ -3579,13 +3570,13 @@
     </row>
     <row r="46" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A46" s="1" t="s">
-        <v>194</v>
+        <v>98</v>
       </c>
       <c r="B46" s="1" t="s">
-        <v>195</v>
+        <v>99</v>
       </c>
       <c r="C46" s="1" t="s">
-        <v>196</v>
+        <v>100</v>
       </c>
       <c r="D46" s="1">
         <v>2</v>
@@ -3596,13 +3587,13 @@
     </row>
     <row r="47" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A47" s="1" t="s">
-        <v>101</v>
+        <v>188</v>
       </c>
       <c r="B47" s="1" t="s">
-        <v>102</v>
+        <v>189</v>
       </c>
       <c r="C47" s="1" t="s">
-        <v>103</v>
+        <v>190</v>
       </c>
       <c r="D47" s="1">
         <v>2</v>
@@ -3613,16 +3604,16 @@
     </row>
     <row r="48" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A48" s="1" t="s">
-        <v>191</v>
+        <v>173</v>
       </c>
       <c r="B48" s="1" t="s">
-        <v>192</v>
+        <v>174</v>
       </c>
       <c r="C48" s="1" t="s">
-        <v>193</v>
+        <v>175</v>
       </c>
       <c r="D48" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E48" s="1">
         <v>1</v>
@@ -3630,16 +3621,16 @@
     </row>
     <row r="49" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A49" s="1" t="s">
-        <v>176</v>
+        <v>65</v>
       </c>
       <c r="B49" s="1" t="s">
-        <v>177</v>
+        <v>66</v>
       </c>
       <c r="C49" s="1" t="s">
-        <v>178</v>
+        <v>67</v>
       </c>
       <c r="D49" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E49" s="1">
         <v>1</v>
@@ -3647,16 +3638,16 @@
     </row>
     <row r="50" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A50" s="1" t="s">
-        <v>68</v>
+        <v>107</v>
       </c>
       <c r="B50" s="1" t="s">
-        <v>69</v>
+        <v>108</v>
       </c>
       <c r="C50" s="1" t="s">
-        <v>70</v>
+        <v>109</v>
       </c>
       <c r="D50" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E50" s="1">
         <v>1</v>
@@ -3664,16 +3655,16 @@
     </row>
     <row r="51" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A51" s="1" t="s">
-        <v>110</v>
+        <v>155</v>
       </c>
       <c r="B51" s="1" t="s">
-        <v>111</v>
+        <v>156</v>
       </c>
       <c r="C51" s="1" t="s">
-        <v>112</v>
+        <v>157</v>
       </c>
       <c r="D51" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E51" s="1">
         <v>1</v>
@@ -3681,16 +3672,16 @@
     </row>
     <row r="52" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A52" s="1" t="s">
-        <v>158</v>
+        <v>119</v>
       </c>
       <c r="B52" s="1" t="s">
-        <v>159</v>
+        <v>120</v>
       </c>
       <c r="C52" s="1" t="s">
-        <v>160</v>
+        <v>121</v>
       </c>
       <c r="D52" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E52" s="1">
         <v>1</v>
@@ -3698,16 +3689,16 @@
     </row>
     <row r="53" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A53" s="1" t="s">
-        <v>122</v>
+        <v>140</v>
       </c>
       <c r="B53" s="1" t="s">
-        <v>123</v>
+        <v>141</v>
       </c>
       <c r="C53" s="1" t="s">
-        <v>124</v>
+        <v>142</v>
       </c>
       <c r="D53" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E53" s="1">
         <v>1</v>
@@ -3715,16 +3706,16 @@
     </row>
     <row r="54" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A54" s="1" t="s">
-        <v>143</v>
+        <v>176</v>
       </c>
       <c r="B54" s="1" t="s">
-        <v>144</v>
+        <v>177</v>
       </c>
       <c r="C54" s="1" t="s">
-        <v>145</v>
+        <v>178</v>
       </c>
       <c r="D54" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E54" s="1">
         <v>1</v>
@@ -3732,16 +3723,16 @@
     </row>
     <row r="55" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A55" s="1" t="s">
-        <v>179</v>
+        <v>83</v>
       </c>
       <c r="B55" s="1" t="s">
-        <v>180</v>
+        <v>84</v>
       </c>
       <c r="C55" s="1" t="s">
-        <v>181</v>
+        <v>85</v>
       </c>
       <c r="D55" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E55" s="1">
         <v>1</v>
@@ -3749,13 +3740,13 @@
     </row>
     <row r="56" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A56" s="1" t="s">
-        <v>86</v>
+        <v>182</v>
       </c>
       <c r="B56" s="1" t="s">
-        <v>87</v>
+        <v>183</v>
       </c>
       <c r="C56" s="1" t="s">
-        <v>88</v>
+        <v>184</v>
       </c>
       <c r="D56" s="1">
         <v>0</v>
@@ -3766,13 +3757,13 @@
     </row>
     <row r="57" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A57" s="1" t="s">
-        <v>185</v>
+        <v>62</v>
       </c>
       <c r="B57" s="1" t="s">
-        <v>186</v>
+        <v>63</v>
       </c>
       <c r="C57" s="1" t="s">
-        <v>187</v>
+        <v>64</v>
       </c>
       <c r="D57" s="1">
         <v>0</v>
@@ -3783,16 +3774,16 @@
     </row>
     <row r="58" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A58" s="1" t="s">
-        <v>65</v>
+        <v>149</v>
       </c>
       <c r="B58" s="1" t="s">
-        <v>66</v>
+        <v>150</v>
       </c>
       <c r="C58" s="1" t="s">
-        <v>67</v>
+        <v>151</v>
       </c>
       <c r="D58" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E58" s="1">
         <v>1</v>
@@ -3800,16 +3791,16 @@
     </row>
     <row r="59" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A59" s="1" t="s">
-        <v>152</v>
+        <v>20</v>
       </c>
       <c r="B59" s="1" t="s">
-        <v>153</v>
+        <v>21</v>
       </c>
       <c r="C59" s="1" t="s">
-        <v>154</v>
+        <v>22</v>
       </c>
       <c r="D59" s="1">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E59" s="1">
         <v>1</v>
@@ -3817,16 +3808,16 @@
     </row>
     <row r="60" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A60" s="1" t="s">
-        <v>23</v>
+        <v>110</v>
       </c>
       <c r="B60" s="1" t="s">
-        <v>24</v>
+        <v>111</v>
       </c>
       <c r="C60" s="1" t="s">
-        <v>25</v>
+        <v>112</v>
       </c>
       <c r="D60" s="1">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E60" s="1">
         <v>1</v>
@@ -3834,16 +3825,16 @@
     </row>
     <row r="61" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A61" s="1" t="s">
-        <v>113</v>
+        <v>205</v>
       </c>
       <c r="B61" s="1" t="s">
-        <v>114</v>
+        <v>206</v>
       </c>
       <c r="C61" s="1" t="s">
-        <v>115</v>
+        <v>207</v>
       </c>
       <c r="D61" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E61" s="1">
         <v>1</v>
@@ -3851,13 +3842,13 @@
     </row>
     <row r="62" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A62" s="1" t="s">
-        <v>208</v>
+        <v>152</v>
       </c>
       <c r="B62" s="1" t="s">
-        <v>209</v>
+        <v>153</v>
       </c>
       <c r="C62" s="1" t="s">
-        <v>210</v>
+        <v>154</v>
       </c>
       <c r="D62" s="1">
         <v>0</v>
@@ -3868,13 +3859,10 @@
     </row>
     <row r="63" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A63" s="1" t="s">
-        <v>155</v>
-      </c>
-      <c r="B63" s="1" t="s">
-        <v>156</v>
+        <v>9</v>
       </c>
       <c r="C63" s="1" t="s">
-        <v>157</v>
+        <v>10</v>
       </c>
       <c r="D63" s="1">
         <v>0</v>
@@ -3885,10 +3873,13 @@
     </row>
     <row r="64" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A64" s="1" t="s">
-        <v>9</v>
+        <v>29</v>
+      </c>
+      <c r="B64" s="1" t="s">
+        <v>30</v>
       </c>
       <c r="C64" s="1" t="s">
-        <v>10</v>
+        <v>31</v>
       </c>
       <c r="D64" s="1">
         <v>0</v>
@@ -3899,13 +3890,13 @@
     </row>
     <row r="65" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A65" s="1" t="s">
-        <v>32</v>
+        <v>89</v>
       </c>
       <c r="B65" s="1" t="s">
-        <v>33</v>
+        <v>90</v>
       </c>
       <c r="C65" s="1" t="s">
-        <v>34</v>
+        <v>91</v>
       </c>
       <c r="D65" s="1">
         <v>0</v>
@@ -3916,13 +3907,13 @@
     </row>
     <row r="66" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A66" s="1" t="s">
-        <v>92</v>
+        <v>26</v>
       </c>
       <c r="B66" s="1" t="s">
-        <v>93</v>
+        <v>27</v>
       </c>
       <c r="C66" s="1" t="s">
-        <v>94</v>
+        <v>28</v>
       </c>
       <c r="D66" s="1">
         <v>0</v>
@@ -3933,16 +3924,16 @@
     </row>
     <row r="67" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A67" s="1" t="s">
-        <v>29</v>
+        <v>92</v>
       </c>
       <c r="B67" s="1" t="s">
-        <v>30</v>
+        <v>93</v>
       </c>
       <c r="C67" s="1" t="s">
-        <v>31</v>
+        <v>94</v>
       </c>
       <c r="D67" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E67" s="1">
         <v>1</v>
@@ -3950,16 +3941,16 @@
     </row>
     <row r="68" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A68" s="1" t="s">
-        <v>95</v>
+        <v>164</v>
       </c>
       <c r="B68" s="1" t="s">
-        <v>96</v>
+        <v>165</v>
       </c>
       <c r="C68" s="1" t="s">
-        <v>97</v>
+        <v>166</v>
       </c>
       <c r="D68" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E68" s="1">
         <v>1</v>
@@ -3967,16 +3958,16 @@
     </row>
     <row r="69" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A69" s="1" t="s">
-        <v>167</v>
+        <v>125</v>
       </c>
       <c r="B69" s="1" t="s">
-        <v>168</v>
+        <v>126</v>
       </c>
       <c r="C69" s="1" t="s">
-        <v>169</v>
+        <v>127</v>
       </c>
       <c r="D69" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E69" s="1">
         <v>1</v>
@@ -3984,13 +3975,13 @@
     </row>
     <row r="70" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A70" s="1" t="s">
-        <v>128</v>
+        <v>122</v>
       </c>
       <c r="B70" s="1" t="s">
-        <v>129</v>
+        <v>123</v>
       </c>
       <c r="C70" s="1" t="s">
-        <v>130</v>
+        <v>124</v>
       </c>
       <c r="D70" s="1">
         <v>1</v>
@@ -4001,30 +3992,30 @@
     </row>
     <row r="71" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A71" s="1" t="s">
-        <v>125</v>
+        <v>232</v>
       </c>
       <c r="B71" s="1" t="s">
-        <v>126</v>
+        <v>233</v>
       </c>
       <c r="C71" s="1" t="s">
-        <v>127</v>
+        <v>234</v>
       </c>
       <c r="D71" s="1">
         <v>1</v>
       </c>
       <c r="E71" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="72" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A72" s="1" t="s">
-        <v>235</v>
+        <v>324</v>
       </c>
       <c r="B72" s="1" t="s">
-        <v>236</v>
+        <v>325</v>
       </c>
       <c r="C72" s="1" t="s">
-        <v>237</v>
+        <v>326</v>
       </c>
       <c r="D72" s="1">
         <v>1</v>
@@ -4035,13 +4026,13 @@
     </row>
     <row r="73" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A73" s="1" t="s">
-        <v>327</v>
+        <v>309</v>
       </c>
       <c r="B73" s="1" t="s">
-        <v>328</v>
+        <v>310</v>
       </c>
       <c r="C73" s="1" t="s">
-        <v>329</v>
+        <v>311</v>
       </c>
       <c r="D73" s="1">
         <v>1</v>
@@ -4052,16 +4043,16 @@
     </row>
     <row r="74" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A74" s="1" t="s">
-        <v>312</v>
+        <v>409</v>
       </c>
       <c r="B74" s="1" t="s">
-        <v>313</v>
+        <v>410</v>
       </c>
       <c r="C74" s="1" t="s">
-        <v>314</v>
+        <v>411</v>
       </c>
       <c r="D74" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E74" s="1">
         <v>2</v>
@@ -4069,16 +4060,16 @@
     </row>
     <row r="75" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A75" s="1" t="s">
-        <v>412</v>
+        <v>460</v>
       </c>
       <c r="B75" s="1" t="s">
-        <v>413</v>
+        <v>461</v>
       </c>
       <c r="C75" s="1" t="s">
-        <v>414</v>
+        <v>462</v>
       </c>
       <c r="D75" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E75" s="1">
         <v>2</v>
@@ -4086,16 +4077,16 @@
     </row>
     <row r="76" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A76" s="1" t="s">
-        <v>463</v>
+        <v>360</v>
       </c>
       <c r="B76" s="1" t="s">
-        <v>464</v>
+        <v>361</v>
       </c>
       <c r="C76" s="1" t="s">
-        <v>465</v>
+        <v>362</v>
       </c>
       <c r="D76" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E76" s="1">
         <v>2</v>
@@ -4103,16 +4094,16 @@
     </row>
     <row r="77" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A77" s="1" t="s">
-        <v>363</v>
+        <v>321</v>
       </c>
       <c r="B77" s="1" t="s">
-        <v>364</v>
+        <v>322</v>
       </c>
       <c r="C77" s="1" t="s">
-        <v>365</v>
+        <v>323</v>
       </c>
       <c r="D77" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E77" s="1">
         <v>2</v>
@@ -4120,16 +4111,16 @@
     </row>
     <row r="78" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A78" s="1" t="s">
-        <v>324</v>
+        <v>351</v>
       </c>
       <c r="B78" s="1" t="s">
-        <v>325</v>
+        <v>352</v>
       </c>
       <c r="C78" s="1" t="s">
-        <v>326</v>
+        <v>353</v>
       </c>
       <c r="D78" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E78" s="1">
         <v>2</v>
@@ -4137,13 +4128,13 @@
     </row>
     <row r="79" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A79" s="1" t="s">
-        <v>354</v>
+        <v>363</v>
       </c>
       <c r="B79" s="1" t="s">
-        <v>355</v>
+        <v>364</v>
       </c>
       <c r="C79" s="1" t="s">
-        <v>356</v>
+        <v>365</v>
       </c>
       <c r="D79" s="1">
         <v>2</v>
@@ -4154,13 +4145,13 @@
     </row>
     <row r="80" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A80" s="1" t="s">
-        <v>366</v>
+        <v>247</v>
       </c>
       <c r="B80" s="1" t="s">
-        <v>367</v>
+        <v>248</v>
       </c>
       <c r="C80" s="1" t="s">
-        <v>368</v>
+        <v>249</v>
       </c>
       <c r="D80" s="1">
         <v>2</v>
@@ -4171,16 +4162,16 @@
     </row>
     <row r="81" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A81" s="1" t="s">
-        <v>250</v>
+        <v>395</v>
       </c>
       <c r="B81" s="1" t="s">
-        <v>251</v>
+        <v>396</v>
       </c>
       <c r="C81" s="1" t="s">
-        <v>252</v>
+        <v>397</v>
       </c>
       <c r="D81" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E81" s="1">
         <v>2</v>
@@ -4188,16 +4179,16 @@
     </row>
     <row r="82" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A82" s="1" t="s">
-        <v>398</v>
+        <v>276</v>
       </c>
       <c r="B82" s="1" t="s">
-        <v>399</v>
+        <v>277</v>
       </c>
       <c r="C82" s="1" t="s">
-        <v>400</v>
+        <v>278</v>
       </c>
       <c r="D82" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E82" s="1">
         <v>2</v>
@@ -4205,16 +4196,16 @@
     </row>
     <row r="83" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A83" s="1" t="s">
-        <v>279</v>
+        <v>454</v>
       </c>
       <c r="B83" s="1" t="s">
-        <v>280</v>
+        <v>455</v>
       </c>
       <c r="C83" s="1" t="s">
-        <v>281</v>
+        <v>456</v>
       </c>
       <c r="D83" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E83" s="1">
         <v>2</v>
@@ -4222,16 +4213,16 @@
     </row>
     <row r="84" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A84" s="1" t="s">
-        <v>457</v>
+        <v>282</v>
       </c>
       <c r="B84" s="1" t="s">
-        <v>458</v>
+        <v>283</v>
       </c>
       <c r="C84" s="1" t="s">
-        <v>459</v>
+        <v>284</v>
       </c>
       <c r="D84" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E84" s="1">
         <v>2</v>
@@ -4239,16 +4230,16 @@
     </row>
     <row r="85" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A85" s="1" t="s">
-        <v>285</v>
+        <v>291</v>
       </c>
       <c r="B85" s="1" t="s">
-        <v>286</v>
+        <v>292</v>
       </c>
       <c r="C85" s="1" t="s">
-        <v>287</v>
+        <v>293</v>
       </c>
       <c r="D85" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E85" s="1">
         <v>2</v>
@@ -4256,16 +4247,16 @@
     </row>
     <row r="86" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A86" s="1" t="s">
-        <v>294</v>
+        <v>297</v>
       </c>
       <c r="B86" s="1" t="s">
-        <v>295</v>
+        <v>298</v>
       </c>
       <c r="C86" s="1" t="s">
-        <v>296</v>
+        <v>299</v>
       </c>
       <c r="D86" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E86" s="1">
         <v>2</v>
@@ -4273,16 +4264,16 @@
     </row>
     <row r="87" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A87" s="1" t="s">
-        <v>300</v>
+        <v>270</v>
       </c>
       <c r="B87" s="1" t="s">
-        <v>301</v>
+        <v>271</v>
       </c>
       <c r="C87" s="1" t="s">
-        <v>302</v>
+        <v>272</v>
       </c>
       <c r="D87" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E87" s="1">
         <v>2</v>
@@ -4290,13 +4281,13 @@
     </row>
     <row r="88" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A88" s="1" t="s">
-        <v>273</v>
+        <v>463</v>
       </c>
       <c r="B88" s="1" t="s">
-        <v>274</v>
+        <v>464</v>
       </c>
       <c r="C88" s="1" t="s">
-        <v>275</v>
+        <v>465</v>
       </c>
       <c r="D88" s="1">
         <v>2</v>
@@ -4307,13 +4298,13 @@
     </row>
     <row r="89" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A89" s="1" t="s">
-        <v>466</v>
+        <v>427</v>
       </c>
       <c r="B89" s="1" t="s">
-        <v>467</v>
+        <v>428</v>
       </c>
       <c r="C89" s="1" t="s">
-        <v>468</v>
+        <v>429</v>
       </c>
       <c r="D89" s="1">
         <v>2</v>
@@ -4324,16 +4315,16 @@
     </row>
     <row r="90" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A90" s="1" t="s">
-        <v>430</v>
+        <v>273</v>
       </c>
       <c r="B90" s="1" t="s">
-        <v>431</v>
+        <v>274</v>
       </c>
       <c r="C90" s="1" t="s">
-        <v>432</v>
+        <v>275</v>
       </c>
       <c r="D90" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E90" s="1">
         <v>2</v>
@@ -4341,13 +4332,13 @@
     </row>
     <row r="91" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A91" s="1" t="s">
-        <v>276</v>
+        <v>451</v>
       </c>
       <c r="B91" s="1" t="s">
-        <v>277</v>
+        <v>452</v>
       </c>
       <c r="C91" s="1" t="s">
-        <v>278</v>
+        <v>453</v>
       </c>
       <c r="D91" s="1">
         <v>1</v>
@@ -4358,16 +4349,16 @@
     </row>
     <row r="92" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A92" s="1" t="s">
-        <v>454</v>
+        <v>436</v>
       </c>
       <c r="B92" s="1" t="s">
-        <v>455</v>
+        <v>437</v>
       </c>
       <c r="C92" s="1" t="s">
-        <v>456</v>
+        <v>438</v>
       </c>
       <c r="D92" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E92" s="1">
         <v>2</v>
@@ -4375,13 +4366,13 @@
     </row>
     <row r="93" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A93" s="1" t="s">
-        <v>439</v>
+        <v>264</v>
       </c>
       <c r="B93" s="1" t="s">
-        <v>440</v>
+        <v>265</v>
       </c>
       <c r="C93" s="1" t="s">
-        <v>441</v>
+        <v>266</v>
       </c>
       <c r="D93" s="1">
         <v>2</v>
@@ -4392,16 +4383,16 @@
     </row>
     <row r="94" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A94" s="1" t="s">
-        <v>267</v>
+        <v>372</v>
       </c>
       <c r="B94" s="1" t="s">
-        <v>268</v>
+        <v>373</v>
       </c>
       <c r="C94" s="1" t="s">
-        <v>269</v>
+        <v>374</v>
       </c>
       <c r="D94" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E94" s="1">
         <v>2</v>
@@ -4409,13 +4400,13 @@
     </row>
     <row r="95" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A95" s="1" t="s">
-        <v>375</v>
+        <v>214</v>
       </c>
       <c r="B95" s="1" t="s">
-        <v>376</v>
+        <v>215</v>
       </c>
       <c r="C95" s="1" t="s">
-        <v>377</v>
+        <v>216</v>
       </c>
       <c r="D95" s="1">
         <v>1</v>
@@ -4426,16 +4417,16 @@
     </row>
     <row r="96" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A96" s="1" t="s">
-        <v>217</v>
+        <v>384</v>
       </c>
       <c r="B96" s="1" t="s">
-        <v>218</v>
+        <v>224</v>
       </c>
       <c r="C96" s="1" t="s">
-        <v>219</v>
+        <v>385</v>
       </c>
       <c r="D96" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E96" s="1">
         <v>2</v>
@@ -4443,13 +4434,13 @@
     </row>
     <row r="97" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A97" s="1" t="s">
-        <v>387</v>
+        <v>439</v>
       </c>
       <c r="B97" s="1" t="s">
-        <v>227</v>
+        <v>440</v>
       </c>
       <c r="C97" s="1" t="s">
-        <v>388</v>
+        <v>441</v>
       </c>
       <c r="D97" s="1">
         <v>2</v>
@@ -4460,16 +4451,16 @@
     </row>
     <row r="98" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A98" s="1" t="s">
-        <v>442</v>
+        <v>229</v>
       </c>
       <c r="B98" s="1" t="s">
-        <v>443</v>
+        <v>230</v>
       </c>
       <c r="C98" s="1" t="s">
-        <v>444</v>
+        <v>231</v>
       </c>
       <c r="D98" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E98" s="1">
         <v>2</v>
@@ -4477,16 +4468,16 @@
     </row>
     <row r="99" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A99" s="1" t="s">
-        <v>232</v>
+        <v>339</v>
       </c>
       <c r="B99" s="1" t="s">
-        <v>233</v>
+        <v>340</v>
       </c>
       <c r="C99" s="1" t="s">
-        <v>234</v>
+        <v>341</v>
       </c>
       <c r="D99" s="1">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E99" s="1">
         <v>2</v>
@@ -4494,16 +4485,16 @@
     </row>
     <row r="100" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A100" s="1" t="s">
-        <v>342</v>
+        <v>244</v>
       </c>
       <c r="B100" s="1" t="s">
-        <v>343</v>
+        <v>245</v>
       </c>
       <c r="C100" s="1" t="s">
-        <v>344</v>
+        <v>246</v>
       </c>
       <c r="D100" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E100" s="1">
         <v>2</v>
@@ -4511,16 +4502,16 @@
     </row>
     <row r="101" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A101" s="1" t="s">
-        <v>247</v>
+        <v>415</v>
       </c>
       <c r="B101" s="1" t="s">
-        <v>248</v>
+        <v>416</v>
       </c>
       <c r="C101" s="1" t="s">
-        <v>249</v>
+        <v>417</v>
       </c>
       <c r="D101" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E101" s="1">
         <v>2</v>
@@ -4528,16 +4519,16 @@
     </row>
     <row r="102" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A102" s="1" t="s">
-        <v>418</v>
+        <v>433</v>
       </c>
       <c r="B102" s="1" t="s">
-        <v>419</v>
+        <v>434</v>
       </c>
       <c r="C102" s="1" t="s">
-        <v>420</v>
+        <v>435</v>
       </c>
       <c r="D102" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E102" s="1">
         <v>2</v>
@@ -4545,16 +4536,16 @@
     </row>
     <row r="103" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A103" s="1" t="s">
-        <v>436</v>
+        <v>403</v>
       </c>
       <c r="B103" s="1" t="s">
-        <v>437</v>
+        <v>404</v>
       </c>
       <c r="C103" s="1" t="s">
-        <v>438</v>
+        <v>405</v>
       </c>
       <c r="D103" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E103" s="1">
         <v>2</v>
@@ -4562,16 +4553,16 @@
     </row>
     <row r="104" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A104" s="1" t="s">
-        <v>406</v>
+        <v>366</v>
       </c>
       <c r="B104" s="1" t="s">
-        <v>407</v>
+        <v>367</v>
       </c>
       <c r="C104" s="1" t="s">
-        <v>408</v>
+        <v>368</v>
       </c>
       <c r="D104" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E104" s="1">
         <v>2</v>
@@ -4588,7 +4579,7 @@
         <v>371</v>
       </c>
       <c r="D105" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E105" s="1">
         <v>2</v>
@@ -4596,13 +4587,13 @@
     </row>
     <row r="106" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A106" s="1" t="s">
-        <v>372</v>
+        <v>389</v>
       </c>
       <c r="B106" s="1" t="s">
-        <v>373</v>
+        <v>390</v>
       </c>
       <c r="C106" s="1" t="s">
-        <v>374</v>
+        <v>391</v>
       </c>
       <c r="D106" s="1">
         <v>1</v>
@@ -4613,16 +4604,16 @@
     </row>
     <row r="107" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A107" s="1" t="s">
-        <v>392</v>
+        <v>412</v>
       </c>
       <c r="B107" s="1" t="s">
-        <v>393</v>
+        <v>413</v>
       </c>
       <c r="C107" s="1" t="s">
-        <v>394</v>
+        <v>414</v>
       </c>
       <c r="D107" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E107" s="1">
         <v>2</v>
@@ -4630,13 +4621,13 @@
     </row>
     <row r="108" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A108" s="1" t="s">
-        <v>415</v>
+        <v>442</v>
       </c>
       <c r="B108" s="1" t="s">
-        <v>416</v>
+        <v>443</v>
       </c>
       <c r="C108" s="1" t="s">
-        <v>417</v>
+        <v>444</v>
       </c>
       <c r="D108" s="1">
         <v>0</v>
@@ -4647,16 +4638,16 @@
     </row>
     <row r="109" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A109" s="1" t="s">
-        <v>445</v>
+        <v>211</v>
       </c>
       <c r="B109" s="1" t="s">
-        <v>446</v>
+        <v>212</v>
       </c>
       <c r="C109" s="1" t="s">
-        <v>447</v>
+        <v>213</v>
       </c>
       <c r="D109" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E109" s="1">
         <v>2</v>
@@ -4664,13 +4655,13 @@
     </row>
     <row r="110" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A110" s="1" t="s">
-        <v>214</v>
+        <v>217</v>
       </c>
       <c r="B110" s="1" t="s">
-        <v>215</v>
+        <v>218</v>
       </c>
       <c r="C110" s="1" t="s">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="D110" s="1">
         <v>2</v>
@@ -4681,16 +4672,16 @@
     </row>
     <row r="111" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A111" s="1" t="s">
-        <v>220</v>
+        <v>457</v>
       </c>
       <c r="B111" s="1" t="s">
-        <v>221</v>
+        <v>458</v>
       </c>
       <c r="C111" s="1" t="s">
-        <v>222</v>
+        <v>459</v>
       </c>
       <c r="D111" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E111" s="1">
         <v>2</v>
@@ -4698,16 +4689,16 @@
     </row>
     <row r="112" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A112" s="1" t="s">
-        <v>460</v>
+        <v>294</v>
       </c>
       <c r="B112" s="1" t="s">
-        <v>461</v>
+        <v>295</v>
       </c>
       <c r="C112" s="1" t="s">
-        <v>462</v>
+        <v>296</v>
       </c>
       <c r="D112" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E112" s="1">
         <v>2</v>
@@ -4715,16 +4706,16 @@
     </row>
     <row r="113" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A113" s="1" t="s">
-        <v>297</v>
+        <v>381</v>
       </c>
       <c r="B113" s="1" t="s">
-        <v>298</v>
+        <v>382</v>
       </c>
       <c r="C113" s="1" t="s">
-        <v>299</v>
+        <v>383</v>
       </c>
       <c r="D113" s="1">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E113" s="1">
         <v>2</v>
@@ -4732,13 +4723,13 @@
     </row>
     <row r="114" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A114" s="1" t="s">
-        <v>384</v>
+        <v>375</v>
       </c>
       <c r="B114" s="1" t="s">
-        <v>385</v>
+        <v>376</v>
       </c>
       <c r="C114" s="1" t="s">
-        <v>386</v>
+        <v>377</v>
       </c>
       <c r="D114" s="1">
         <v>3</v>
@@ -4749,16 +4740,16 @@
     </row>
     <row r="115" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A115" s="1" t="s">
-        <v>378</v>
+        <v>223</v>
       </c>
       <c r="B115" s="1" t="s">
-        <v>379</v>
+        <v>224</v>
       </c>
       <c r="C115" s="1" t="s">
-        <v>380</v>
+        <v>225</v>
       </c>
       <c r="D115" s="1">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E115" s="1">
         <v>2</v>
@@ -4766,13 +4757,13 @@
     </row>
     <row r="116" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A116" s="1" t="s">
-        <v>226</v>
+        <v>235</v>
       </c>
       <c r="B116" s="1" t="s">
-        <v>227</v>
+        <v>236</v>
       </c>
       <c r="C116" s="1" t="s">
-        <v>228</v>
+        <v>237</v>
       </c>
       <c r="D116" s="1">
         <v>1</v>
@@ -4783,13 +4774,13 @@
     </row>
     <row r="117" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A117" s="1" t="s">
-        <v>238</v>
+        <v>327</v>
       </c>
       <c r="B117" s="1" t="s">
-        <v>239</v>
+        <v>328</v>
       </c>
       <c r="C117" s="1" t="s">
-        <v>240</v>
+        <v>329</v>
       </c>
       <c r="D117" s="1">
         <v>1</v>
@@ -4800,16 +4791,16 @@
     </row>
     <row r="118" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A118" s="1" t="s">
-        <v>330</v>
+        <v>445</v>
       </c>
       <c r="B118" s="1" t="s">
-        <v>331</v>
+        <v>446</v>
       </c>
       <c r="C118" s="1" t="s">
-        <v>332</v>
+        <v>447</v>
       </c>
       <c r="D118" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E118" s="1">
         <v>2</v>
@@ -4817,13 +4808,13 @@
     </row>
     <row r="119" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A119" s="1" t="s">
-        <v>448</v>
+        <v>267</v>
       </c>
       <c r="B119" s="1" t="s">
-        <v>449</v>
+        <v>268</v>
       </c>
       <c r="C119" s="1" t="s">
-        <v>450</v>
+        <v>269</v>
       </c>
       <c r="D119" s="1">
         <v>2</v>
@@ -4834,16 +4825,16 @@
     </row>
     <row r="120" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A120" s="1" t="s">
-        <v>270</v>
+        <v>300</v>
       </c>
       <c r="B120" s="1" t="s">
-        <v>271</v>
+        <v>301</v>
       </c>
       <c r="C120" s="1" t="s">
-        <v>272</v>
+        <v>302</v>
       </c>
       <c r="D120" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E120" s="1">
         <v>2</v>
@@ -4851,16 +4842,16 @@
     </row>
     <row r="121" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A121" s="1" t="s">
-        <v>303</v>
+        <v>430</v>
       </c>
       <c r="B121" s="1" t="s">
-        <v>304</v>
+        <v>431</v>
       </c>
       <c r="C121" s="1" t="s">
-        <v>305</v>
+        <v>432</v>
       </c>
       <c r="D121" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E121" s="1">
         <v>2</v>
@@ -4868,16 +4859,16 @@
     </row>
     <row r="122" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A122" s="1" t="s">
-        <v>433</v>
+        <v>418</v>
       </c>
       <c r="B122" s="1" t="s">
-        <v>434</v>
+        <v>419</v>
       </c>
       <c r="C122" s="1" t="s">
-        <v>435</v>
+        <v>420</v>
       </c>
       <c r="D122" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E122" s="1">
         <v>2</v>
@@ -4885,16 +4876,16 @@
     </row>
     <row r="123" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A123" s="1" t="s">
-        <v>421</v>
+        <v>241</v>
       </c>
       <c r="B123" s="1" t="s">
-        <v>422</v>
+        <v>242</v>
       </c>
       <c r="C123" s="1" t="s">
-        <v>423</v>
+        <v>243</v>
       </c>
       <c r="D123" s="1">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E123" s="1">
         <v>2</v>
@@ -4902,16 +4893,16 @@
     </row>
     <row r="124" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A124" s="1" t="s">
-        <v>244</v>
+        <v>220</v>
       </c>
       <c r="B124" s="1" t="s">
-        <v>245</v>
+        <v>221</v>
       </c>
       <c r="C124" s="1" t="s">
-        <v>246</v>
+        <v>222</v>
       </c>
       <c r="D124" s="1">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E124" s="1">
         <v>2</v>
@@ -4919,13 +4910,13 @@
     </row>
     <row r="125" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A125" s="1" t="s">
-        <v>223</v>
+        <v>421</v>
       </c>
       <c r="B125" s="1" t="s">
-        <v>224</v>
+        <v>422</v>
       </c>
       <c r="C125" s="1" t="s">
-        <v>225</v>
+        <v>423</v>
       </c>
       <c r="D125" s="1">
         <v>0</v>
@@ -4936,13 +4927,13 @@
     </row>
     <row r="126" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A126" s="1" t="s">
-        <v>424</v>
+        <v>288</v>
       </c>
       <c r="B126" s="1" t="s">
-        <v>425</v>
+        <v>289</v>
       </c>
       <c r="C126" s="1" t="s">
-        <v>426</v>
+        <v>290</v>
       </c>
       <c r="D126" s="1">
         <v>0</v>
@@ -4953,16 +4944,16 @@
     </row>
     <row r="127" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A127" s="1" t="s">
-        <v>291</v>
+        <v>401</v>
       </c>
       <c r="B127" s="1" t="s">
-        <v>292</v>
+        <v>168</v>
       </c>
       <c r="C127" s="1" t="s">
-        <v>293</v>
+        <v>402</v>
       </c>
       <c r="D127" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E127" s="1">
         <v>2</v>
@@ -4970,13 +4961,13 @@
     </row>
     <row r="128" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A128" s="1" t="s">
-        <v>404</v>
+        <v>303</v>
       </c>
       <c r="B128" s="1" t="s">
-        <v>171</v>
+        <v>304</v>
       </c>
       <c r="C128" s="1" t="s">
-        <v>405</v>
+        <v>305</v>
       </c>
       <c r="D128" s="1">
         <v>1</v>
@@ -4987,16 +4978,16 @@
     </row>
     <row r="129" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A129" s="1" t="s">
-        <v>306</v>
+        <v>226</v>
       </c>
       <c r="B129" s="1" t="s">
-        <v>307</v>
+        <v>227</v>
       </c>
       <c r="C129" s="1" t="s">
-        <v>308</v>
+        <v>228</v>
       </c>
       <c r="D129" s="1">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E129" s="1">
         <v>2</v>
@@ -5004,16 +4995,16 @@
     </row>
     <row r="130" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A130" s="1" t="s">
-        <v>229</v>
+        <v>448</v>
       </c>
       <c r="B130" s="1" t="s">
-        <v>230</v>
+        <v>449</v>
       </c>
       <c r="C130" s="1" t="s">
-        <v>231</v>
+        <v>450</v>
       </c>
       <c r="D130" s="1">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E130" s="1">
         <v>2</v>
@@ -5021,13 +5012,13 @@
     </row>
     <row r="131" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A131" s="1" t="s">
-        <v>451</v>
+        <v>285</v>
       </c>
       <c r="B131" s="1" t="s">
-        <v>452</v>
+        <v>286</v>
       </c>
       <c r="C131" s="1" t="s">
-        <v>453</v>
+        <v>287</v>
       </c>
       <c r="D131" s="1">
         <v>1</v>
@@ -5038,16 +5029,16 @@
     </row>
     <row r="132" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A132" s="1" t="s">
-        <v>288</v>
+        <v>238</v>
       </c>
       <c r="B132" s="1" t="s">
-        <v>289</v>
+        <v>239</v>
       </c>
       <c r="C132" s="1" t="s">
-        <v>290</v>
+        <v>240</v>
       </c>
       <c r="D132" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E132" s="1">
         <v>2</v>
@@ -5055,16 +5046,16 @@
     </row>
     <row r="133" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A133" s="1" t="s">
-        <v>241</v>
+        <v>336</v>
       </c>
       <c r="B133" s="1" t="s">
-        <v>242</v>
+        <v>337</v>
       </c>
       <c r="C133" s="1" t="s">
-        <v>243</v>
+        <v>338</v>
       </c>
       <c r="D133" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E133" s="1">
         <v>2</v>
@@ -5072,16 +5063,16 @@
     </row>
     <row r="134" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A134" s="1" t="s">
-        <v>339</v>
+        <v>424</v>
       </c>
       <c r="B134" s="1" t="s">
-        <v>340</v>
+        <v>425</v>
       </c>
       <c r="C134" s="1" t="s">
-        <v>341</v>
+        <v>426</v>
       </c>
       <c r="D134" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E134" s="1">
         <v>2</v>
@@ -5089,16 +5080,16 @@
     </row>
     <row r="135" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A135" s="1" t="s">
-        <v>427</v>
+        <v>315</v>
       </c>
       <c r="B135" s="1" t="s">
-        <v>428</v>
+        <v>316</v>
       </c>
       <c r="C135" s="1" t="s">
-        <v>429</v>
+        <v>317</v>
       </c>
       <c r="D135" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E135" s="1">
         <v>2</v>
@@ -5123,16 +5114,16 @@
     </row>
     <row r="137" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A137" s="1" t="s">
-        <v>321</v>
+        <v>406</v>
       </c>
       <c r="B137" s="1" t="s">
-        <v>322</v>
+        <v>407</v>
       </c>
       <c r="C137" s="1" t="s">
-        <v>323</v>
+        <v>408</v>
       </c>
       <c r="D137" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E137" s="1">
         <v>2</v>
@@ -5140,16 +5131,16 @@
     </row>
     <row r="138" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A138" s="1" t="s">
-        <v>409</v>
+        <v>250</v>
       </c>
       <c r="B138" s="1" t="s">
-        <v>410</v>
+        <v>251</v>
       </c>
       <c r="C138" s="1" t="s">
-        <v>411</v>
+        <v>252</v>
       </c>
       <c r="D138" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E138" s="1">
         <v>2</v>
@@ -5157,16 +5148,16 @@
     </row>
     <row r="139" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A139" s="1" t="s">
-        <v>253</v>
+        <v>345</v>
       </c>
       <c r="B139" s="1" t="s">
-        <v>254</v>
+        <v>346</v>
       </c>
       <c r="C139" s="1" t="s">
-        <v>255</v>
+        <v>347</v>
       </c>
       <c r="D139" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E139" s="1">
         <v>2</v>
@@ -5174,16 +5165,16 @@
     </row>
     <row r="140" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A140" s="1" t="s">
-        <v>348</v>
+        <v>261</v>
       </c>
       <c r="B140" s="1" t="s">
-        <v>349</v>
+        <v>262</v>
       </c>
       <c r="C140" s="1" t="s">
-        <v>350</v>
+        <v>263</v>
       </c>
       <c r="D140" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E140" s="1">
         <v>2</v>
@@ -5191,13 +5182,13 @@
     </row>
     <row r="141" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A141" s="1" t="s">
-        <v>264</v>
+        <v>357</v>
       </c>
       <c r="B141" s="1" t="s">
-        <v>265</v>
+        <v>358</v>
       </c>
       <c r="C141" s="1" t="s">
-        <v>266</v>
+        <v>359</v>
       </c>
       <c r="D141" s="1">
         <v>2</v>
@@ -5208,16 +5199,16 @@
     </row>
     <row r="142" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A142" s="1" t="s">
-        <v>360</v>
+        <v>312</v>
       </c>
       <c r="B142" s="1" t="s">
-        <v>361</v>
+        <v>313</v>
       </c>
       <c r="C142" s="1" t="s">
-        <v>362</v>
+        <v>314</v>
       </c>
       <c r="D142" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E142" s="1">
         <v>2</v>
@@ -5225,16 +5216,16 @@
     </row>
     <row r="143" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A143" s="1" t="s">
-        <v>315</v>
+        <v>392</v>
       </c>
       <c r="B143" s="1" t="s">
-        <v>316</v>
+        <v>393</v>
       </c>
       <c r="C143" s="1" t="s">
-        <v>317</v>
+        <v>394</v>
       </c>
       <c r="D143" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E143" s="1">
         <v>2</v>
@@ -5242,16 +5233,16 @@
     </row>
     <row r="144" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A144" s="1" t="s">
-        <v>395</v>
+        <v>306</v>
       </c>
       <c r="B144" s="1" t="s">
-        <v>396</v>
+        <v>307</v>
       </c>
       <c r="C144" s="1" t="s">
-        <v>397</v>
+        <v>308</v>
       </c>
       <c r="D144" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E144" s="1">
         <v>2</v>
@@ -5259,13 +5250,13 @@
     </row>
     <row r="145" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A145" s="1" t="s">
-        <v>309</v>
+        <v>398</v>
       </c>
       <c r="B145" s="1" t="s">
-        <v>310</v>
+        <v>399</v>
       </c>
       <c r="C145" s="1" t="s">
-        <v>311</v>
+        <v>400</v>
       </c>
       <c r="D145" s="1">
         <v>1</v>
@@ -5276,13 +5267,13 @@
     </row>
     <row r="146" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A146" s="1" t="s">
-        <v>401</v>
+        <v>333</v>
       </c>
       <c r="B146" s="1" t="s">
-        <v>402</v>
+        <v>334</v>
       </c>
       <c r="C146" s="1" t="s">
-        <v>403</v>
+        <v>335</v>
       </c>
       <c r="D146" s="1">
         <v>1</v>
@@ -5293,13 +5284,13 @@
     </row>
     <row r="147" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A147" s="1" t="s">
-        <v>336</v>
+        <v>279</v>
       </c>
       <c r="B147" s="1" t="s">
-        <v>337</v>
+        <v>280</v>
       </c>
       <c r="C147" s="1" t="s">
-        <v>338</v>
+        <v>281</v>
       </c>
       <c r="D147" s="1">
         <v>1</v>
@@ -5310,16 +5301,16 @@
     </row>
     <row r="148" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A148" s="1" t="s">
-        <v>282</v>
+        <v>256</v>
       </c>
       <c r="B148" s="1" t="s">
-        <v>283</v>
+        <v>257</v>
       </c>
       <c r="C148" s="1" t="s">
-        <v>284</v>
+        <v>258</v>
       </c>
       <c r="D148" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E148" s="1">
         <v>2</v>
@@ -5327,16 +5318,16 @@
     </row>
     <row r="149" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A149" s="1" t="s">
-        <v>259</v>
+        <v>253</v>
       </c>
       <c r="B149" s="1" t="s">
-        <v>260</v>
+        <v>254</v>
       </c>
       <c r="C149" s="1" t="s">
-        <v>261</v>
+        <v>255</v>
       </c>
       <c r="D149" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E149" s="1">
         <v>2</v>
@@ -5344,13 +5335,13 @@
     </row>
     <row r="150" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A150" s="1" t="s">
-        <v>256</v>
+        <v>208</v>
       </c>
       <c r="B150" s="1" t="s">
-        <v>257</v>
+        <v>209</v>
       </c>
       <c r="C150" s="1" t="s">
-        <v>258</v>
+        <v>210</v>
       </c>
       <c r="D150" s="1">
         <v>2</v>
@@ -5361,16 +5352,16 @@
     </row>
     <row r="151" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A151" s="1" t="s">
-        <v>211</v>
+        <v>354</v>
       </c>
       <c r="B151" s="1" t="s">
-        <v>212</v>
+        <v>355</v>
       </c>
       <c r="C151" s="1" t="s">
-        <v>213</v>
+        <v>356</v>
       </c>
       <c r="D151" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E151" s="1">
         <v>2</v>
@@ -5378,16 +5369,16 @@
     </row>
     <row r="152" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A152" s="1" t="s">
-        <v>357</v>
+        <v>348</v>
       </c>
       <c r="B152" s="1" t="s">
-        <v>358</v>
+        <v>349</v>
       </c>
       <c r="C152" s="1" t="s">
-        <v>359</v>
+        <v>350</v>
       </c>
       <c r="D152" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E152" s="1">
         <v>2</v>
@@ -5395,16 +5386,16 @@
     </row>
     <row r="153" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A153" s="1" t="s">
-        <v>351</v>
+        <v>330</v>
       </c>
       <c r="B153" s="1" t="s">
-        <v>352</v>
+        <v>331</v>
       </c>
       <c r="C153" s="1" t="s">
-        <v>353</v>
+        <v>332</v>
       </c>
       <c r="D153" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E153" s="1">
         <v>2</v>
@@ -5412,16 +5403,16 @@
     </row>
     <row r="154" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A154" s="1" t="s">
-        <v>333</v>
+        <v>259</v>
       </c>
       <c r="B154" s="1" t="s">
-        <v>334</v>
+        <v>260</v>
       </c>
       <c r="C154" s="1" t="s">
-        <v>335</v>
+        <v>258</v>
       </c>
       <c r="D154" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E154" s="1">
         <v>2</v>
@@ -5429,16 +5420,16 @@
     </row>
     <row r="155" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A155" s="1" t="s">
-        <v>262</v>
+        <v>386</v>
       </c>
       <c r="B155" s="1" t="s">
-        <v>263</v>
+        <v>387</v>
       </c>
       <c r="C155" s="1" t="s">
-        <v>261</v>
+        <v>388</v>
       </c>
       <c r="D155" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E155" s="1">
         <v>2</v>
@@ -5446,16 +5437,16 @@
     </row>
     <row r="156" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A156" s="1" t="s">
-        <v>389</v>
+        <v>378</v>
       </c>
       <c r="B156" s="1" t="s">
-        <v>390</v>
+        <v>379</v>
       </c>
       <c r="C156" s="1" t="s">
-        <v>391</v>
+        <v>380</v>
       </c>
       <c r="D156" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E156" s="1">
         <v>2</v>
@@ -5463,16 +5454,16 @@
     </row>
     <row r="157" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A157" s="1" t="s">
-        <v>381</v>
+        <v>342</v>
       </c>
       <c r="B157" s="1" t="s">
-        <v>382</v>
+        <v>343</v>
       </c>
       <c r="C157" s="1" t="s">
-        <v>383</v>
+        <v>344</v>
       </c>
       <c r="D157" s="1">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E157" s="1">
         <v>2</v>
@@ -5480,33 +5471,33 @@
     </row>
     <row r="158" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A158" s="1" t="s">
-        <v>345</v>
+        <v>501</v>
       </c>
       <c r="B158" s="1" t="s">
-        <v>346</v>
+        <v>502</v>
       </c>
       <c r="C158" s="1" t="s">
-        <v>347</v>
+        <v>503</v>
       </c>
       <c r="D158" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E158" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="159" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A159" s="1" t="s">
-        <v>504</v>
+        <v>495</v>
       </c>
       <c r="B159" s="1" t="s">
-        <v>505</v>
+        <v>496</v>
       </c>
       <c r="C159" s="1" t="s">
-        <v>506</v>
+        <v>497</v>
       </c>
       <c r="D159" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E159" s="1">
         <v>3</v>
@@ -5531,13 +5522,13 @@
     </row>
     <row r="161" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A161" s="1" t="s">
-        <v>501</v>
+        <v>537</v>
       </c>
       <c r="B161" s="1" t="s">
-        <v>502</v>
+        <v>538</v>
       </c>
       <c r="C161" s="1" t="s">
-        <v>503</v>
+        <v>539</v>
       </c>
       <c r="D161" s="1">
         <v>1</v>
@@ -5548,13 +5539,13 @@
     </row>
     <row r="162" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A162" s="1" t="s">
-        <v>540</v>
+        <v>534</v>
       </c>
       <c r="B162" s="1" t="s">
-        <v>541</v>
+        <v>535</v>
       </c>
       <c r="C162" s="1" t="s">
-        <v>542</v>
+        <v>536</v>
       </c>
       <c r="D162" s="1">
         <v>1</v>
@@ -5565,13 +5556,13 @@
     </row>
     <row r="163" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A163" s="1" t="s">
-        <v>537</v>
+        <v>540</v>
       </c>
       <c r="B163" s="1" t="s">
-        <v>538</v>
+        <v>541</v>
       </c>
       <c r="C163" s="1" t="s">
-        <v>539</v>
+        <v>542</v>
       </c>
       <c r="D163" s="1">
         <v>1</v>
@@ -5582,13 +5573,13 @@
     </row>
     <row r="164" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A164" s="1" t="s">
-        <v>543</v>
+        <v>522</v>
       </c>
       <c r="B164" s="1" t="s">
-        <v>544</v>
+        <v>523</v>
       </c>
       <c r="C164" s="1" t="s">
-        <v>545</v>
+        <v>524</v>
       </c>
       <c r="D164" s="1">
         <v>1</v>
@@ -5599,16 +5590,16 @@
     </row>
     <row r="165" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A165" s="1" t="s">
-        <v>525</v>
+        <v>504</v>
       </c>
       <c r="B165" s="1" t="s">
-        <v>526</v>
+        <v>505</v>
       </c>
       <c r="C165" s="1" t="s">
-        <v>527</v>
+        <v>506</v>
       </c>
       <c r="D165" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E165" s="1">
         <v>3</v>
@@ -5616,13 +5607,13 @@
     </row>
     <row r="166" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A166" s="1" t="s">
-        <v>507</v>
+        <v>486</v>
       </c>
       <c r="B166" s="1" t="s">
-        <v>508</v>
+        <v>487</v>
       </c>
       <c r="C166" s="1" t="s">
-        <v>509</v>
+        <v>488</v>
       </c>
       <c r="D166" s="1">
         <v>2</v>
@@ -5633,16 +5624,16 @@
     </row>
     <row r="167" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A167" s="1" t="s">
-        <v>489</v>
+        <v>480</v>
       </c>
       <c r="B167" s="1" t="s">
-        <v>490</v>
+        <v>481</v>
       </c>
       <c r="C167" s="1" t="s">
-        <v>491</v>
+        <v>482</v>
       </c>
       <c r="D167" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E167" s="1">
         <v>3</v>
@@ -5650,16 +5641,16 @@
     </row>
     <row r="168" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A168" s="1" t="s">
-        <v>483</v>
+        <v>489</v>
       </c>
       <c r="B168" s="1" t="s">
-        <v>484</v>
+        <v>490</v>
       </c>
       <c r="C168" s="1" t="s">
-        <v>485</v>
+        <v>491</v>
       </c>
       <c r="D168" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E168" s="1">
         <v>3</v>
@@ -5667,16 +5658,16 @@
     </row>
     <row r="169" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A169" s="1" t="s">
-        <v>492</v>
+        <v>513</v>
       </c>
       <c r="B169" s="1" t="s">
-        <v>493</v>
+        <v>514</v>
       </c>
       <c r="C169" s="1" t="s">
-        <v>494</v>
+        <v>515</v>
       </c>
       <c r="D169" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E169" s="1">
         <v>3</v>
@@ -5684,16 +5675,16 @@
     </row>
     <row r="170" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A170" s="1" t="s">
-        <v>516</v>
+        <v>492</v>
       </c>
       <c r="B170" s="1" t="s">
-        <v>517</v>
+        <v>493</v>
       </c>
       <c r="C170" s="1" t="s">
-        <v>518</v>
+        <v>494</v>
       </c>
       <c r="D170" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E170" s="1">
         <v>3</v>
@@ -5701,13 +5692,13 @@
     </row>
     <row r="171" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A171" s="1" t="s">
-        <v>495</v>
+        <v>466</v>
       </c>
       <c r="B171" s="1" t="s">
-        <v>496</v>
+        <v>467</v>
       </c>
       <c r="C171" s="1" t="s">
-        <v>497</v>
+        <v>468</v>
       </c>
       <c r="D171" s="1">
         <v>2</v>
@@ -5718,13 +5709,13 @@
     </row>
     <row r="172" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A172" s="1" t="s">
-        <v>469</v>
+        <v>478</v>
       </c>
       <c r="B172" s="1" t="s">
-        <v>470</v>
+        <v>292</v>
       </c>
       <c r="C172" s="1" t="s">
-        <v>471</v>
+        <v>479</v>
       </c>
       <c r="D172" s="1">
         <v>2</v>
@@ -5735,16 +5726,16 @@
     </row>
     <row r="173" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A173" s="1" t="s">
-        <v>481</v>
+        <v>546</v>
       </c>
       <c r="B173" s="1" t="s">
-        <v>295</v>
+        <v>547</v>
       </c>
       <c r="C173" s="1" t="s">
-        <v>482</v>
+        <v>548</v>
       </c>
       <c r="D173" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E173" s="1">
         <v>3</v>
@@ -5752,16 +5743,16 @@
     </row>
     <row r="174" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A174" s="1" t="s">
-        <v>549</v>
+        <v>469</v>
       </c>
       <c r="B174" s="1" t="s">
-        <v>550</v>
+        <v>470</v>
       </c>
       <c r="C174" s="1" t="s">
-        <v>551</v>
+        <v>471</v>
       </c>
       <c r="D174" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E174" s="1">
         <v>3</v>
@@ -5769,13 +5760,13 @@
     </row>
     <row r="175" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A175" s="1" t="s">
-        <v>472</v>
+        <v>475</v>
       </c>
       <c r="B175" s="1" t="s">
-        <v>473</v>
+        <v>476</v>
       </c>
       <c r="C175" s="1" t="s">
-        <v>474</v>
+        <v>477</v>
       </c>
       <c r="D175" s="1">
         <v>2</v>
@@ -5786,13 +5777,13 @@
     </row>
     <row r="176" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A176" s="1" t="s">
-        <v>478</v>
+        <v>519</v>
       </c>
       <c r="B176" s="1" t="s">
-        <v>479</v>
+        <v>520</v>
       </c>
       <c r="C176" s="1" t="s">
-        <v>480</v>
+        <v>521</v>
       </c>
       <c r="D176" s="1">
         <v>2</v>
@@ -5803,16 +5794,16 @@
     </row>
     <row r="177" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A177" s="1" t="s">
-        <v>522</v>
+        <v>543</v>
       </c>
       <c r="B177" s="1" t="s">
-        <v>523</v>
+        <v>544</v>
       </c>
       <c r="C177" s="1" t="s">
-        <v>524</v>
+        <v>545</v>
       </c>
       <c r="D177" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E177" s="1">
         <v>3</v>
@@ -5820,16 +5811,16 @@
     </row>
     <row r="178" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A178" s="1" t="s">
-        <v>546</v>
+        <v>516</v>
       </c>
       <c r="B178" s="1" t="s">
-        <v>547</v>
+        <v>517</v>
       </c>
       <c r="C178" s="1" t="s">
-        <v>548</v>
+        <v>518</v>
       </c>
       <c r="D178" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E178" s="1">
         <v>3</v>
@@ -5837,16 +5828,16 @@
     </row>
     <row r="179" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A179" s="1" t="s">
-        <v>519</v>
+        <v>531</v>
       </c>
       <c r="B179" s="1" t="s">
-        <v>520</v>
+        <v>532</v>
       </c>
       <c r="C179" s="1" t="s">
-        <v>521</v>
+        <v>533</v>
       </c>
       <c r="D179" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E179" s="1">
         <v>3</v>
@@ -5854,13 +5845,13 @@
     </row>
     <row r="180" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A180" s="1" t="s">
-        <v>534</v>
+        <v>525</v>
       </c>
       <c r="B180" s="1" t="s">
-        <v>535</v>
+        <v>526</v>
       </c>
       <c r="C180" s="1" t="s">
-        <v>536</v>
+        <v>527</v>
       </c>
       <c r="D180" s="1">
         <v>1</v>
@@ -5871,13 +5862,13 @@
     </row>
     <row r="181" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A181" s="1" t="s">
-        <v>528</v>
+        <v>483</v>
       </c>
       <c r="B181" s="1" t="s">
-        <v>529</v>
+        <v>484</v>
       </c>
       <c r="C181" s="1" t="s">
-        <v>530</v>
+        <v>485</v>
       </c>
       <c r="D181" s="1">
         <v>1</v>
@@ -5888,16 +5879,16 @@
     </row>
     <row r="182" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A182" s="1" t="s">
-        <v>486</v>
+        <v>507</v>
       </c>
       <c r="B182" s="1" t="s">
-        <v>487</v>
+        <v>508</v>
       </c>
       <c r="C182" s="1" t="s">
-        <v>488</v>
+        <v>509</v>
       </c>
       <c r="D182" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E182" s="1">
         <v>3</v>
@@ -5905,16 +5896,16 @@
     </row>
     <row r="183" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A183" s="1" t="s">
-        <v>510</v>
+        <v>528</v>
       </c>
       <c r="B183" s="1" t="s">
-        <v>511</v>
+        <v>529</v>
       </c>
       <c r="C183" s="1" t="s">
-        <v>512</v>
+        <v>530</v>
       </c>
       <c r="D183" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E183" s="1">
         <v>3</v>
@@ -5922,16 +5913,16 @@
     </row>
     <row r="184" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A184" s="1" t="s">
-        <v>531</v>
+        <v>472</v>
       </c>
       <c r="B184" s="1" t="s">
-        <v>532</v>
+        <v>473</v>
       </c>
       <c r="C184" s="1" t="s">
-        <v>533</v>
+        <v>474</v>
       </c>
       <c r="D184" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E184" s="1">
         <v>3</v>
@@ -5939,16 +5930,16 @@
     </row>
     <row r="185" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A185" s="1" t="s">
-        <v>475</v>
+        <v>510</v>
       </c>
       <c r="B185" s="1" t="s">
-        <v>476</v>
+        <v>511</v>
       </c>
       <c r="C185" s="1" t="s">
-        <v>477</v>
+        <v>512</v>
       </c>
       <c r="D185" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E185" s="1">
         <v>3</v>
@@ -5956,13 +5947,13 @@
     </row>
     <row r="186" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A186" s="1" t="s">
-        <v>513</v>
+        <v>549</v>
       </c>
       <c r="B186" s="1" t="s">
-        <v>514</v>
+        <v>550</v>
       </c>
       <c r="C186" s="1" t="s">
-        <v>515</v>
+        <v>551</v>
       </c>
       <c r="D186" s="1">
         <v>1</v>
@@ -5973,33 +5964,33 @@
     </row>
     <row r="187" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A187" s="1" t="s">
-        <v>552</v>
+        <v>567</v>
       </c>
       <c r="B187" s="1" t="s">
-        <v>553</v>
+        <v>568</v>
       </c>
       <c r="C187" s="1" t="s">
-        <v>554</v>
+        <v>569</v>
       </c>
       <c r="D187" s="1">
         <v>1</v>
       </c>
       <c r="E187" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="188" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A188" s="1" t="s">
-        <v>570</v>
+        <v>555</v>
       </c>
       <c r="B188" s="1" t="s">
-        <v>571</v>
+        <v>556</v>
       </c>
       <c r="C188" s="1" t="s">
-        <v>572</v>
+        <v>557</v>
       </c>
       <c r="D188" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E188" s="1">
         <v>4</v>
@@ -6007,13 +5998,13 @@
     </row>
     <row r="189" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A189" s="1" t="s">
-        <v>558</v>
+        <v>564</v>
       </c>
       <c r="B189" s="1" t="s">
-        <v>559</v>
+        <v>565</v>
       </c>
       <c r="C189" s="1" t="s">
-        <v>560</v>
+        <v>566</v>
       </c>
       <c r="D189" s="1">
         <v>2</v>
@@ -6024,16 +6015,16 @@
     </row>
     <row r="190" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A190" s="1" t="s">
-        <v>567</v>
+        <v>558</v>
       </c>
       <c r="B190" s="1" t="s">
-        <v>568</v>
+        <v>559</v>
       </c>
       <c r="C190" s="1" t="s">
-        <v>569</v>
+        <v>560</v>
       </c>
       <c r="D190" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E190" s="1">
         <v>4</v>
@@ -6058,16 +6049,16 @@
     </row>
     <row r="192" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A192" s="1" t="s">
-        <v>564</v>
+        <v>579</v>
       </c>
       <c r="B192" s="1" t="s">
-        <v>565</v>
+        <v>580</v>
       </c>
       <c r="C192" s="1" t="s">
-        <v>566</v>
+        <v>581</v>
       </c>
       <c r="D192" s="1">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E192" s="1">
         <v>4</v>
@@ -6075,16 +6066,16 @@
     </row>
     <row r="193" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A193" s="1" t="s">
-        <v>582</v>
+        <v>576</v>
       </c>
       <c r="B193" s="1" t="s">
-        <v>583</v>
+        <v>577</v>
       </c>
       <c r="C193" s="1" t="s">
-        <v>584</v>
+        <v>578</v>
       </c>
       <c r="D193" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E193" s="1">
         <v>4</v>
@@ -6092,16 +6083,16 @@
     </row>
     <row r="194" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A194" s="1" t="s">
-        <v>579</v>
+        <v>588</v>
       </c>
       <c r="B194" s="1" t="s">
-        <v>580</v>
+        <v>589</v>
       </c>
       <c r="C194" s="1" t="s">
-        <v>581</v>
+        <v>590</v>
       </c>
       <c r="D194" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E194" s="1">
         <v>4</v>
@@ -6109,16 +6100,16 @@
     </row>
     <row r="195" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A195" s="1" t="s">
-        <v>591</v>
+        <v>585</v>
       </c>
       <c r="B195" s="1" t="s">
-        <v>592</v>
+        <v>586</v>
       </c>
       <c r="C195" s="1" t="s">
-        <v>593</v>
+        <v>587</v>
       </c>
       <c r="D195" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E195" s="1">
         <v>4</v>
@@ -6126,16 +6117,16 @@
     </row>
     <row r="196" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A196" s="1" t="s">
-        <v>588</v>
+        <v>573</v>
       </c>
       <c r="B196" s="1" t="s">
-        <v>589</v>
+        <v>574</v>
       </c>
       <c r="C196" s="1" t="s">
-        <v>590</v>
+        <v>575</v>
       </c>
       <c r="D196" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E196" s="1">
         <v>4</v>
@@ -6143,16 +6134,16 @@
     </row>
     <row r="197" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A197" s="1" t="s">
-        <v>576</v>
+        <v>570</v>
       </c>
       <c r="B197" s="1" t="s">
-        <v>577</v>
+        <v>571</v>
       </c>
       <c r="C197" s="1" t="s">
-        <v>578</v>
+        <v>572</v>
       </c>
       <c r="D197" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E197" s="1">
         <v>4</v>
@@ -6160,16 +6151,16 @@
     </row>
     <row r="198" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A198" s="1" t="s">
-        <v>573</v>
+        <v>582</v>
       </c>
       <c r="B198" s="1" t="s">
-        <v>574</v>
+        <v>583</v>
       </c>
       <c r="C198" s="1" t="s">
-        <v>575</v>
+        <v>584</v>
       </c>
       <c r="D198" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E198" s="1">
         <v>4</v>
@@ -6177,13 +6168,13 @@
     </row>
     <row r="199" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A199" s="1" t="s">
-        <v>585</v>
+        <v>552</v>
       </c>
       <c r="B199" s="1" t="s">
-        <v>586</v>
+        <v>553</v>
       </c>
       <c r="C199" s="1" t="s">
-        <v>587</v>
+        <v>554</v>
       </c>
       <c r="D199" s="1">
         <v>0</v>
@@ -6194,30 +6185,30 @@
     </row>
     <row r="200" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A200" s="1" t="s">
-        <v>555</v>
+        <v>591</v>
       </c>
       <c r="B200" s="1" t="s">
-        <v>556</v>
+        <v>592</v>
       </c>
       <c r="C200" s="1" t="s">
-        <v>557</v>
+        <v>593</v>
       </c>
       <c r="D200" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E200" s="1">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="201" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A201" s="1" t="s">
-        <v>594</v>
+        <v>596</v>
       </c>
       <c r="B201" s="1" t="s">
-        <v>595</v>
+        <v>597</v>
       </c>
       <c r="C201" s="1" t="s">
-        <v>596</v>
+        <v>598</v>
       </c>
       <c r="D201" s="1">
         <v>1</v>
@@ -6237,7 +6228,7 @@
         <v>601</v>
       </c>
       <c r="D202" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E202" s="1">
         <v>5</v>
@@ -6245,13 +6236,13 @@
     </row>
     <row r="203" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A203" s="1" t="s">
-        <v>602</v>
+        <v>594</v>
       </c>
       <c r="B203" s="1" t="s">
-        <v>603</v>
+        <v>511</v>
       </c>
       <c r="C203" s="1" t="s">
-        <v>604</v>
+        <v>595</v>
       </c>
       <c r="D203" s="1">
         <v>2</v>
@@ -6262,19 +6253,19 @@
     </row>
     <row r="204" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A204" s="1" t="s">
-        <v>597</v>
+        <v>602</v>
       </c>
       <c r="B204" s="1" t="s">
-        <v>514</v>
+        <v>603</v>
       </c>
       <c r="C204" s="1" t="s">
-        <v>598</v>
+        <v>604</v>
       </c>
       <c r="D204" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E204" s="1">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="205" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.2">
@@ -6291,31 +6282,14 @@
         <v>1</v>
       </c>
       <c r="E205" s="1">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="206" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A206" s="1" t="s">
-        <v>608</v>
-      </c>
-      <c r="B206" s="1" t="s">
-        <v>609</v>
-      </c>
-      <c r="C206" s="1" t="s">
-        <v>610</v>
-      </c>
-      <c r="D206" s="1">
-        <v>1</v>
-      </c>
-      <c r="E206" s="1">
         <v>7</v>
       </c>
     </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A3:E206">
-    <sortCondition ref="E3:E206"/>
-    <sortCondition ref="A3:A206"/>
-    <sortCondition ref="D3:D206"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A3:E205">
+    <sortCondition ref="E3:E205"/>
+    <sortCondition ref="A3:A205"/>
+    <sortCondition ref="D3:D205"/>
   </sortState>
   <phoneticPr fontId="18" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
